--- a/reports/Debug-purgatory-20260104/For The Day (Actual)_Payroll.xlsx
+++ b/reports/Debug-purgatory-20260104/For The Day (Actual)_Payroll.xlsx
@@ -14,135 +14,141 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1586" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1590" uniqueCount="309">
   <si>
     <t>eecode</t>
   </si>
   <si>
+    <t>A4DB</t>
+  </si>
+  <si>
+    <t>A3LM</t>
+  </si>
+  <si>
+    <t>A4CG</t>
+  </si>
+  <si>
     <t>J520</t>
   </si>
   <si>
+    <t>A06T</t>
+  </si>
+  <si>
+    <t>A3DX</t>
+  </si>
+  <si>
+    <t>A3Q0</t>
+  </si>
+  <si>
+    <t>J072</t>
+  </si>
+  <si>
+    <t>A3NT</t>
+  </si>
+  <si>
+    <t>A3T7</t>
+  </si>
+  <si>
+    <t>A4AN</t>
+  </si>
+  <si>
+    <t>A4B0</t>
+  </si>
+  <si>
+    <t>A3GJ</t>
+  </si>
+  <si>
+    <t>A0DO</t>
+  </si>
+  <si>
+    <t>B197</t>
+  </si>
+  <si>
+    <t>F683</t>
+  </si>
+  <si>
+    <t>A0CX</t>
+  </si>
+  <si>
+    <t>E075</t>
+  </si>
+  <si>
     <t>A3RS</t>
   </si>
   <si>
-    <t>A0CX</t>
-  </si>
-  <si>
-    <t>A3DX</t>
-  </si>
-  <si>
-    <t>A4DB</t>
+    <t>A44A</t>
+  </si>
+  <si>
+    <t>J158</t>
+  </si>
+  <si>
+    <t>J399</t>
+  </si>
+  <si>
+    <t>A0XN</t>
   </si>
   <si>
     <t>A2JJ</t>
   </si>
   <si>
-    <t>A3GJ</t>
-  </si>
-  <si>
-    <t>A4B0</t>
-  </si>
-  <si>
-    <t>A4AN</t>
-  </si>
-  <si>
-    <t>A3T7</t>
-  </si>
-  <si>
-    <t>A3NT</t>
-  </si>
-  <si>
-    <t>A4CG</t>
-  </si>
-  <si>
-    <t>A3LM</t>
-  </si>
-  <si>
-    <t>A0XN</t>
-  </si>
-  <si>
-    <t>J072</t>
-  </si>
-  <si>
-    <t>A3Q0</t>
-  </si>
-  <si>
-    <t>A44A</t>
-  </si>
-  <si>
-    <t>J158</t>
-  </si>
-  <si>
-    <t>F683</t>
-  </si>
-  <si>
-    <t>A0DO</t>
-  </si>
-  <si>
-    <t>J399</t>
-  </si>
-  <si>
-    <t>A06T</t>
-  </si>
-  <si>
-    <t>E075</t>
-  </si>
-  <si>
-    <t>B197</t>
-  </si>
-  <si>
     <t>F406</t>
   </si>
   <si>
+    <t>A4HS</t>
+  </si>
+  <si>
+    <t>B903</t>
+  </si>
+  <si>
+    <t>D519</t>
+  </si>
+  <si>
     <t>A1JS</t>
   </si>
   <si>
-    <t>D519</t>
-  </si>
-  <si>
-    <t>B903</t>
-  </si>
-  <si>
-    <t>A4HS</t>
+    <t>A3PC</t>
+  </si>
+  <si>
+    <t>F499</t>
+  </si>
+  <si>
+    <t>A3P7</t>
+  </si>
+  <si>
+    <t>A1CM</t>
+  </si>
+  <si>
+    <t>A3IL</t>
+  </si>
+  <si>
+    <t>G397</t>
+  </si>
+  <si>
+    <t>A449</t>
+  </si>
+  <si>
+    <t>B696</t>
   </si>
   <si>
     <t>A2HF</t>
   </si>
   <si>
-    <t>A3IL</t>
-  </si>
-  <si>
-    <t>G397</t>
-  </si>
-  <si>
-    <t>B696</t>
-  </si>
-  <si>
-    <t>A449</t>
-  </si>
-  <si>
-    <t>A3PC</t>
-  </si>
-  <si>
-    <t>F499</t>
-  </si>
-  <si>
-    <t>A3P7</t>
-  </si>
-  <si>
-    <t>A1CM</t>
+    <t>A609</t>
+  </si>
+  <si>
+    <t>A0FD</t>
+  </si>
+  <si>
+    <t>J056</t>
   </si>
   <si>
     <t>A3DS</t>
   </si>
   <si>
-    <t>J056</t>
-  </si>
-  <si>
-    <t>A609</t>
-  </si>
-  <si>
-    <t>A0FD</t>
+    <t>A23C</t>
+  </si>
+  <si>
+    <t>E877</t>
   </si>
   <si>
     <t>B250</t>
@@ -151,121 +157,160 @@
     <t>C653</t>
   </si>
   <si>
-    <t>A23C</t>
-  </si>
-  <si>
-    <t>E877</t>
-  </si>
-  <si>
     <t>E135</t>
   </si>
   <si>
+    <t>I524</t>
+  </si>
+  <si>
     <t>J185</t>
   </si>
   <si>
+    <t>A3DR</t>
+  </si>
+  <si>
     <t>E720</t>
   </si>
   <si>
-    <t>I524</t>
-  </si>
-  <si>
-    <t>A3DR</t>
+    <t>D843</t>
+  </si>
+  <si>
+    <t>I762</t>
+  </si>
+  <si>
+    <t>A0JG</t>
   </si>
   <si>
     <t>J471</t>
   </si>
   <si>
+    <t>C208</t>
+  </si>
+  <si>
+    <t>E950</t>
+  </si>
+  <si>
     <t>A3L3</t>
   </si>
   <si>
+    <t>A0JI</t>
+  </si>
+  <si>
+    <t>J467</t>
+  </si>
+  <si>
+    <t>D855</t>
+  </si>
+  <si>
+    <t>A3LN</t>
+  </si>
+  <si>
+    <t>B924</t>
+  </si>
+  <si>
+    <t>B847</t>
+  </si>
+  <si>
+    <t>B898</t>
+  </si>
+  <si>
+    <t>A2H9</t>
+  </si>
+  <si>
+    <t>C132</t>
+  </si>
+  <si>
     <t>A07R</t>
   </si>
   <si>
-    <t>C132</t>
-  </si>
-  <si>
-    <t>J467</t>
-  </si>
-  <si>
-    <t>E950</t>
-  </si>
-  <si>
-    <t>C208</t>
+    <t>J442</t>
   </si>
   <si>
     <t>A889</t>
   </si>
   <si>
-    <t>A2H9</t>
-  </si>
-  <si>
-    <t>B898</t>
-  </si>
-  <si>
-    <t>D843</t>
-  </si>
-  <si>
-    <t>I762</t>
-  </si>
-  <si>
-    <t>J442</t>
-  </si>
-  <si>
-    <t>A0JG</t>
-  </si>
-  <si>
-    <t>A0JI</t>
-  </si>
-  <si>
-    <t>A3LN</t>
-  </si>
-  <si>
-    <t>B847</t>
-  </si>
-  <si>
-    <t>B924</t>
-  </si>
-  <si>
-    <t>D855</t>
+    <t>A3NW</t>
+  </si>
+  <si>
+    <t>A2KR</t>
+  </si>
+  <si>
+    <t>A2TY</t>
+  </si>
+  <si>
+    <t>A2O6</t>
+  </si>
+  <si>
+    <t>E547</t>
+  </si>
+  <si>
+    <t>I563</t>
   </si>
   <si>
     <t>A37H</t>
   </si>
   <si>
-    <t>I563</t>
+    <t>A0XR</t>
+  </si>
+  <si>
+    <t>A44B</t>
+  </si>
+  <si>
+    <t>H586</t>
+  </si>
+  <si>
+    <t>A22D</t>
+  </si>
+  <si>
+    <t>A37N</t>
+  </si>
+  <si>
+    <t>A1FE</t>
+  </si>
+  <si>
+    <t>A34H</t>
+  </si>
+  <si>
+    <t>D110</t>
+  </si>
+  <si>
+    <t>A3O1</t>
+  </si>
+  <si>
+    <t>A3NZ</t>
+  </si>
+  <si>
+    <t>A3OT</t>
   </si>
   <si>
     <t>A3TH</t>
   </si>
   <si>
+    <t>A44D</t>
+  </si>
+  <si>
+    <t>A4FA</t>
+  </si>
+  <si>
+    <t>A15K</t>
+  </si>
+  <si>
+    <t>A1IU</t>
+  </si>
+  <si>
+    <t>A45Q</t>
+  </si>
+  <si>
+    <t>A3ZX</t>
+  </si>
+  <si>
+    <t>A3RC</t>
+  </si>
+  <si>
     <t>A45T</t>
   </si>
   <si>
-    <t>A2O6</t>
-  </si>
-  <si>
-    <t>A22D</t>
-  </si>
-  <si>
-    <t>A44B</t>
-  </si>
-  <si>
-    <t>A2KR</t>
-  </si>
-  <si>
-    <t>A2TY</t>
-  </si>
-  <si>
-    <t>A3ZX</t>
-  </si>
-  <si>
-    <t>A15K</t>
-  </si>
-  <si>
-    <t>A3NZ</t>
-  </si>
-  <si>
-    <t>H586</t>
+    <t>D441</t>
   </si>
   <si>
     <t>A3G3</t>
@@ -274,222 +319,177 @@
     <t>A3HJ</t>
   </si>
   <si>
+    <t>A3NV</t>
+  </si>
+  <si>
     <t>A3M1</t>
   </si>
   <si>
-    <t>A3NV</t>
-  </si>
-  <si>
-    <t>A3RC</t>
-  </si>
-  <si>
-    <t>A45Q</t>
-  </si>
-  <si>
-    <t>A3O1</t>
-  </si>
-  <si>
-    <t>D110</t>
-  </si>
-  <si>
-    <t>A3NW</t>
-  </si>
-  <si>
-    <t>E547</t>
-  </si>
-  <si>
-    <t>A37N</t>
-  </si>
-  <si>
-    <t>A1FE</t>
-  </si>
-  <si>
-    <t>D441</t>
-  </si>
-  <si>
-    <t>A1IU</t>
-  </si>
-  <si>
-    <t>A34H</t>
-  </si>
-  <si>
-    <t>A0XR</t>
-  </si>
-  <si>
-    <t>A3OT</t>
-  </si>
-  <si>
-    <t>A44D</t>
-  </si>
-  <si>
-    <t>A4FA</t>
+    <t>A46W</t>
+  </si>
+  <si>
+    <t>A3KK</t>
+  </si>
+  <si>
+    <t>A3K5</t>
+  </si>
+  <si>
+    <t>A1WX</t>
+  </si>
+  <si>
+    <t>A3C9</t>
   </si>
   <si>
     <t>A3JR</t>
   </si>
   <si>
-    <t>A3C9</t>
-  </si>
-  <si>
-    <t>A1WX</t>
+    <t>A3JG</t>
+  </si>
+  <si>
+    <t>A4AZ</t>
+  </si>
+  <si>
+    <t>A44E</t>
   </si>
   <si>
     <t>A0S2</t>
   </si>
   <si>
+    <t>A3UW</t>
+  </si>
+  <si>
     <t>E587</t>
   </si>
   <si>
     <t>A4FK</t>
   </si>
   <si>
-    <t>A3UW</t>
-  </si>
-  <si>
-    <t>A4AZ</t>
+    <t>A3IU</t>
   </si>
   <si>
     <t>A3TL</t>
   </si>
   <si>
+    <t>G179</t>
+  </si>
+  <si>
+    <t>A3L0</t>
+  </si>
+  <si>
     <t>A3NS</t>
   </si>
   <si>
-    <t>A3L0</t>
+    <t>D243</t>
+  </si>
+  <si>
+    <t>A3JF</t>
+  </si>
+  <si>
+    <t>A2HH</t>
+  </si>
+  <si>
+    <t>A36Y</t>
+  </si>
+  <si>
+    <t>G931</t>
+  </si>
+  <si>
+    <t>H009</t>
+  </si>
+  <si>
+    <t>B360</t>
+  </si>
+  <si>
+    <t>A3JO</t>
+  </si>
+  <si>
+    <t>G877</t>
+  </si>
+  <si>
+    <t>A0QT</t>
+  </si>
+  <si>
+    <t>A2G8</t>
+  </si>
+  <si>
+    <t>A3J7</t>
+  </si>
+  <si>
+    <t>A29N</t>
   </si>
   <si>
     <t>A0FQ</t>
   </si>
   <si>
-    <t>A36Y</t>
-  </si>
-  <si>
-    <t>A2HH</t>
-  </si>
-  <si>
-    <t>G179</t>
+    <t>H209</t>
+  </si>
+  <si>
+    <t>D407</t>
+  </si>
+  <si>
+    <t>C655</t>
+  </si>
+  <si>
+    <t>C013</t>
+  </si>
+  <si>
+    <t>A2D7</t>
   </si>
   <si>
     <t>A3U6</t>
   </si>
   <si>
-    <t>A2D7</t>
-  </si>
-  <si>
-    <t>A29N</t>
-  </si>
-  <si>
-    <t>D407</t>
-  </si>
-  <si>
-    <t>A3JO</t>
-  </si>
-  <si>
-    <t>A3KK</t>
-  </si>
-  <si>
-    <t>A3K5</t>
-  </si>
-  <si>
-    <t>A3JG</t>
-  </si>
-  <si>
-    <t>A3JF</t>
-  </si>
-  <si>
-    <t>A3IU</t>
-  </si>
-  <si>
-    <t>H009</t>
-  </si>
-  <si>
-    <t>G931</t>
-  </si>
-  <si>
     <t>A46U</t>
   </si>
   <si>
-    <t>C013</t>
-  </si>
-  <si>
-    <t>C655</t>
-  </si>
-  <si>
-    <t>H209</t>
-  </si>
-  <si>
-    <t>A0QT</t>
-  </si>
-  <si>
-    <t>A2G8</t>
-  </si>
-  <si>
-    <t>A3J7</t>
-  </si>
-  <si>
-    <t>D243</t>
-  </si>
-  <si>
-    <t>A44E</t>
-  </si>
-  <si>
-    <t>A46W</t>
-  </si>
-  <si>
-    <t>G877</t>
-  </si>
-  <si>
-    <t>B360</t>
+    <t>A4A6</t>
   </si>
   <si>
     <t>A45U</t>
   </si>
   <si>
-    <t>A4A6</t>
-  </si>
-  <si>
     <t>I308</t>
   </si>
   <si>
+    <t>A2LP</t>
+  </si>
+  <si>
     <t>A2AA</t>
   </si>
   <si>
     <t>A0G3</t>
   </si>
   <si>
-    <t>A2LP</t>
+    <t>A37A</t>
+  </si>
+  <si>
+    <t>A3UA</t>
+  </si>
+  <si>
+    <t>A739</t>
+  </si>
+  <si>
+    <t>A4BI</t>
+  </si>
+  <si>
+    <t>B101</t>
+  </si>
+  <si>
+    <t>I424</t>
+  </si>
+  <si>
+    <t>A4GZ</t>
   </si>
   <si>
     <t>B444</t>
   </si>
   <si>
-    <t>A3UA</t>
-  </si>
-  <si>
-    <t>A37A</t>
-  </si>
-  <si>
-    <t>I424</t>
-  </si>
-  <si>
-    <t>A4GZ</t>
-  </si>
-  <si>
     <t>C789</t>
   </si>
   <si>
-    <t>B101</t>
-  </si>
-  <si>
     <t>A19P</t>
   </si>
   <si>
-    <t>A4BI</t>
-  </si>
-  <si>
-    <t>A739</t>
-  </si>
-  <si>
     <t>A4F3</t>
   </si>
   <si>
@@ -502,226 +502,226 @@
     <t>A3FO</t>
   </si>
   <si>
+    <t>A4G3</t>
+  </si>
+  <si>
     <t>A36T</t>
   </si>
   <si>
-    <t>A4G3</t>
+    <t>J434</t>
+  </si>
+  <si>
+    <t>A3H7</t>
+  </si>
+  <si>
+    <t>A4BG</t>
+  </si>
+  <si>
+    <t>A326</t>
+  </si>
+  <si>
+    <t>A1MU</t>
+  </si>
+  <si>
+    <t>A2SG</t>
+  </si>
+  <si>
+    <t>A21H</t>
+  </si>
+  <si>
+    <t>A3GZ</t>
+  </si>
+  <si>
+    <t>I216</t>
+  </si>
+  <si>
+    <t>A3QR</t>
   </si>
   <si>
     <t>J335</t>
   </si>
   <si>
-    <t>A326</t>
-  </si>
-  <si>
-    <t>A2SG</t>
-  </si>
-  <si>
-    <t>A3QR</t>
-  </si>
-  <si>
-    <t>A1MU</t>
-  </si>
-  <si>
-    <t>I216</t>
+    <t>A4D0</t>
   </si>
   <si>
     <t>I518</t>
   </si>
   <si>
-    <t>A3H7</t>
-  </si>
-  <si>
-    <t>A4BG</t>
-  </si>
-  <si>
-    <t>A21H</t>
-  </si>
-  <si>
-    <t>A3GZ</t>
-  </si>
-  <si>
-    <t>A4D0</t>
-  </si>
-  <si>
-    <t>J434</t>
-  </si>
-  <si>
     <t>A3G6</t>
   </si>
   <si>
+    <t>A2BK</t>
+  </si>
+  <si>
+    <t>A3VR</t>
+  </si>
+  <si>
+    <t>A42F</t>
+  </si>
+  <si>
+    <t>A3K9</t>
+  </si>
+  <si>
+    <t>A3Q8</t>
+  </si>
+  <si>
+    <t>A43Z</t>
+  </si>
+  <si>
+    <t>D499</t>
+  </si>
+  <si>
     <t>E001</t>
   </si>
   <si>
+    <t>D274</t>
+  </si>
+  <si>
+    <t>A3GE</t>
+  </si>
+  <si>
+    <t>I956</t>
+  </si>
+  <si>
+    <t>I182</t>
+  </si>
+  <si>
+    <t>A2RM</t>
+  </si>
+  <si>
+    <t>A15N</t>
+  </si>
+  <si>
+    <t>A0XV</t>
+  </si>
+  <si>
+    <t>A4BJ</t>
+  </si>
+  <si>
     <t>A47N</t>
   </si>
   <si>
-    <t>A2BK</t>
-  </si>
-  <si>
-    <t>A3GE</t>
-  </si>
-  <si>
-    <t>D274</t>
-  </si>
-  <si>
-    <t>D499</t>
-  </si>
-  <si>
-    <t>A42F</t>
-  </si>
-  <si>
-    <t>A3K9</t>
-  </si>
-  <si>
-    <t>A3Q8</t>
-  </si>
-  <si>
-    <t>A43Z</t>
-  </si>
-  <si>
-    <t>A4BJ</t>
-  </si>
-  <si>
-    <t>A0XV</t>
-  </si>
-  <si>
-    <t>A15N</t>
-  </si>
-  <si>
-    <t>A2RM</t>
-  </si>
-  <si>
-    <t>I182</t>
-  </si>
-  <si>
-    <t>I956</t>
-  </si>
-  <si>
     <t>A3LI</t>
   </si>
   <si>
-    <t>A3VR</t>
-  </si>
-  <si>
     <t>A49C</t>
   </si>
   <si>
     <t>A3K4</t>
   </si>
   <si>
+    <t>A3DP</t>
+  </si>
+  <si>
+    <t>F313</t>
+  </si>
+  <si>
+    <t>A1N1</t>
+  </si>
+  <si>
+    <t>A3OC</t>
+  </si>
+  <si>
     <t>I810</t>
   </si>
   <si>
-    <t>A3DP</t>
-  </si>
-  <si>
-    <t>F313</t>
-  </si>
-  <si>
-    <t>A1N1</t>
-  </si>
-  <si>
-    <t>A3OC</t>
+    <t>F312</t>
+  </si>
+  <si>
+    <t>J489</t>
+  </si>
+  <si>
+    <t>E608</t>
+  </si>
+  <si>
+    <t>H341</t>
   </si>
   <si>
     <t>J492</t>
   </si>
   <si>
-    <t>E608</t>
-  </si>
-  <si>
-    <t>J489</t>
-  </si>
-  <si>
-    <t>H341</t>
-  </si>
-  <si>
-    <t>F312</t>
-  </si>
-  <si>
     <t>A3FH</t>
   </si>
   <si>
+    <t>A3HI</t>
+  </si>
+  <si>
     <t>A2DH</t>
   </si>
   <si>
-    <t>A3HI</t>
-  </si>
-  <si>
     <t>A3HC</t>
   </si>
   <si>
+    <t>A2RO</t>
+  </si>
+  <si>
+    <t>A40T</t>
+  </si>
+  <si>
+    <t>E609</t>
+  </si>
+  <si>
+    <t>D736</t>
+  </si>
+  <si>
+    <t>F518</t>
+  </si>
+  <si>
+    <t>D071</t>
+  </si>
+  <si>
+    <t>A46X</t>
+  </si>
+  <si>
+    <t>A2SD</t>
+  </si>
+  <si>
+    <t>A37G</t>
+  </si>
+  <si>
+    <t>A2UO</t>
+  </si>
+  <si>
+    <t>A0HT</t>
+  </si>
+  <si>
     <t>A3PE</t>
   </si>
   <si>
-    <t>A2UO</t>
-  </si>
-  <si>
-    <t>A0HT</t>
+    <t>A1WB</t>
   </si>
   <si>
     <t>E080</t>
   </si>
   <si>
-    <t>A46X</t>
-  </si>
-  <si>
-    <t>D071</t>
-  </si>
-  <si>
-    <t>A2RO</t>
-  </si>
-  <si>
-    <t>F518</t>
-  </si>
-  <si>
-    <t>A37G</t>
-  </si>
-  <si>
-    <t>A2SD</t>
-  </si>
-  <si>
     <t>A1MW</t>
   </si>
   <si>
-    <t>A1WB</t>
-  </si>
-  <si>
-    <t>E609</t>
-  </si>
-  <si>
-    <t>D736</t>
-  </si>
-  <si>
-    <t>A40T</t>
+    <t>F240</t>
+  </si>
+  <si>
+    <t>A3X1</t>
+  </si>
+  <si>
+    <t>G316</t>
+  </si>
+  <si>
+    <t>A3SY</t>
+  </si>
+  <si>
+    <t>A2BI</t>
+  </si>
+  <si>
+    <t>A2RJ</t>
   </si>
   <si>
     <t>A3F1</t>
   </si>
   <si>
-    <t>A2RJ</t>
-  </si>
-  <si>
-    <t>A3X1</t>
-  </si>
-  <si>
-    <t>F240</t>
-  </si>
-  <si>
-    <t>G316</t>
-  </si>
-  <si>
-    <t>A2BI</t>
-  </si>
-  <si>
-    <t>A3SY</t>
+    <t>G322</t>
   </si>
   <si>
     <t>A1Z8</t>
-  </si>
-  <si>
-    <t>G322</t>
   </si>
   <si>
     <t>A0AQ</t>
@@ -1354,13 +1354,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>46026.29090277778</v>
+        <v>46026.42520833333</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D2" s="2">
-        <v>46026.70054398148</v>
+        <v>46026.68758101852</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>247</v>
@@ -1369,7 +1369,7 @@
         <v>250</v>
       </c>
       <c r="G2" s="2">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="H2" s="2">
         <v>0</v>
@@ -1386,13 +1386,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="2">
-        <v>46026.40016203704</v>
+        <v>46026.30292824074</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D3" s="2">
-        <v>46026.69107638889</v>
+        <v>46026.6812037037</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>247</v>
@@ -1418,13 +1418,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="2">
-        <v>46026.32672453704</v>
+        <v>46026.31798611111</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D4" s="2">
-        <v>46026.68783564815</v>
+        <v>46026.65792824074</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>247</v>
@@ -1433,7 +1433,7 @@
         <v>250</v>
       </c>
       <c r="G4" s="2">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="H4" s="2">
         <v>0</v>
@@ -1450,13 +1450,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="2">
-        <v>46026.30063657407</v>
+        <v>46026.29090277778</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D5" s="2">
-        <v>46026.69081018519</v>
+        <v>46026.70054398148</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>247</v>
@@ -1465,7 +1465,7 @@
         <v>250</v>
       </c>
       <c r="G5" s="2">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="H5" s="2">
         <v>0</v>
@@ -1482,13 +1482,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="2">
-        <v>46026.42520833333</v>
+        <v>46026.32681712963</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D6" s="2">
-        <v>46026.68758101852</v>
+        <v>46026.69834490741</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>247</v>
@@ -1497,7 +1497,7 @@
         <v>250</v>
       </c>
       <c r="G6" s="2">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="H6" s="2">
         <v>0</v>
@@ -1514,13 +1514,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>46026.3009375</v>
+        <v>46026.30063657407</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D7" s="2">
-        <v>46026.69065972222</v>
+        <v>46026.69081018519</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>247</v>
@@ -1529,7 +1529,7 @@
         <v>250</v>
       </c>
       <c r="G7" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H7" s="2">
         <v>0</v>
@@ -1546,13 +1546,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="2">
-        <v>46026.28856481481</v>
+        <v>46026.31084490741</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D8" s="2">
-        <v>46026.7006712963</v>
+        <v>46026.69869212963</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>247</v>
@@ -1561,7 +1561,7 @@
         <v>250</v>
       </c>
       <c r="G8" s="2">
-        <v>18.5</v>
+        <v>15.16</v>
       </c>
       <c r="H8" s="2">
         <v>0</v>
@@ -1578,13 +1578,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>46026.375</v>
+        <v>46026.31858796296</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D9" s="2">
-        <v>46026.68539351852</v>
+        <v>46026.68585648148</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>247</v>
@@ -1610,13 +1610,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="2">
-        <v>46026.31097222222</v>
+        <v>46026.31888888889</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D10" s="2">
-        <v>46026.68809027778</v>
+        <v>46026.68229166666</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>247</v>
@@ -1674,13 +1674,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>46026.31888888889</v>
+        <v>46026.31097222222</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D12" s="2">
-        <v>46026.68229166666</v>
+        <v>46026.68809027778</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>247</v>
@@ -1706,13 +1706,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>46026.31798611111</v>
+        <v>46026.375</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D13" s="2">
-        <v>46026.65792824074</v>
+        <v>46026.68539351852</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>247</v>
@@ -1738,13 +1738,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>46026.30292824074</v>
+        <v>46026.28856481481</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D14" s="2">
-        <v>46026.6812037037</v>
+        <v>46026.7006712963</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>247</v>
@@ -1753,7 +1753,7 @@
         <v>250</v>
       </c>
       <c r="G14" s="2">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="H14" s="2">
         <v>0</v>
@@ -1770,13 +1770,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="2">
-        <v>46026.32510416667</v>
+        <v>46026.28958333333</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D15" s="2">
-        <v>46026.68086805556</v>
+        <v>46026.69446759259</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>247</v>
@@ -1802,13 +1802,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="2">
-        <v>46026.31858796296</v>
+        <v>46026.29903935185</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D16" s="2">
-        <v>46026.68585648148</v>
+        <v>46026.68994212963</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>247</v>
@@ -1817,7 +1817,7 @@
         <v>250</v>
       </c>
       <c r="G16" s="2">
-        <v>16</v>
+        <v>20.61</v>
       </c>
       <c r="H16" s="2">
         <v>0</v>
@@ -1834,13 +1834,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="2">
-        <v>46026.31084490741</v>
+        <v>46026.31839120371</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D17" s="2">
-        <v>46026.69869212963</v>
+        <v>46026.69371527778</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>247</v>
@@ -1849,7 +1849,7 @@
         <v>250</v>
       </c>
       <c r="G17" s="2">
-        <v>15.16</v>
+        <v>16.5</v>
       </c>
       <c r="H17" s="2">
         <v>0</v>
@@ -1866,13 +1866,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="2">
-        <v>46026.31076388889</v>
+        <v>46026.32672453704</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D18" s="2">
-        <v>46026.68195601852</v>
+        <v>46026.68783564815</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>247</v>
@@ -1881,7 +1881,7 @@
         <v>250</v>
       </c>
       <c r="G18" s="2">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="H18" s="2">
         <v>0</v>
@@ -1898,13 +1898,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="2">
-        <v>46026.3203587963</v>
+        <v>46026.2924537037</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D19" s="2">
-        <v>46026.68177083333</v>
+        <v>46026.6904050926</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>247</v>
@@ -1913,7 +1913,7 @@
         <v>250</v>
       </c>
       <c r="G19" s="2">
-        <v>15.25</v>
+        <v>18.5</v>
       </c>
       <c r="H19" s="2">
         <v>0</v>
@@ -1930,13 +1930,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="2">
-        <v>46026.31839120371</v>
+        <v>46026.40016203704</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D20" s="2">
-        <v>46026.69371527778</v>
+        <v>46026.69107638889</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>247</v>
@@ -1945,7 +1945,7 @@
         <v>250</v>
       </c>
       <c r="G20" s="2">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="H20" s="2">
         <v>0</v>
@@ -1962,13 +1962,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="2">
-        <v>46026.28958333333</v>
+        <v>46026.31076388889</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D21" s="2">
-        <v>46026.69446759259</v>
+        <v>46026.68195601852</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>247</v>
@@ -1977,7 +1977,7 @@
         <v>250</v>
       </c>
       <c r="G21" s="2">
-        <v>16.25</v>
+        <v>16</v>
       </c>
       <c r="H21" s="2">
         <v>0</v>
@@ -1994,13 +1994,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="2">
-        <v>46026.31473379629</v>
+        <v>46026.3203587963</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D22" s="2">
-        <v>46026.68709490741</v>
+        <v>46026.68177083333</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>247</v>
@@ -2009,7 +2009,7 @@
         <v>250</v>
       </c>
       <c r="G22" s="2">
-        <v>16.5</v>
+        <v>15.25</v>
       </c>
       <c r="H22" s="2">
         <v>0</v>
@@ -2026,13 +2026,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="2">
-        <v>46026.32681712963</v>
+        <v>46026.31473379629</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D23" s="2">
-        <v>46026.69834490741</v>
+        <v>46026.68709490741</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>247</v>
@@ -2058,13 +2058,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="2">
-        <v>46026.2924537037</v>
+        <v>46026.32510416667</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D24" s="2">
-        <v>46026.6904050926</v>
+        <v>46026.68086805556</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>247</v>
@@ -2073,7 +2073,7 @@
         <v>250</v>
       </c>
       <c r="G24" s="2">
-        <v>18.5</v>
+        <v>16.25</v>
       </c>
       <c r="H24" s="2">
         <v>0</v>
@@ -2090,13 +2090,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="2">
-        <v>46026.29903935185</v>
+        <v>46026.3009375</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D25" s="2">
-        <v>46026.68994212963</v>
+        <v>46026.69065972222</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>247</v>
@@ -2105,7 +2105,7 @@
         <v>250</v>
       </c>
       <c r="G25" s="2">
-        <v>20.61</v>
+        <v>20</v>
       </c>
       <c r="H25" s="2">
         <v>0</v>
@@ -2154,13 +2154,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="2">
-        <v>46026.27777777778</v>
+        <v>46026.27083333334</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D27" s="2">
-        <v>46026.68976851852</v>
+        <v>46026.69851851852</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>247</v>
@@ -2169,7 +2169,7 @@
         <v>251</v>
       </c>
       <c r="G27" s="2">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="H27" s="2">
         <v>0</v>
@@ -2186,13 +2186,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="2">
-        <v>46026.26789351852</v>
+        <v>46026.26969907407</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D28" s="2">
-        <v>46026.69395833334</v>
+        <v>46026.68943287037</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>247</v>
@@ -2201,7 +2201,7 @@
         <v>251</v>
       </c>
       <c r="G28" s="2">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H28" s="2">
         <v>0</v>
@@ -2218,13 +2218,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="2">
-        <v>46026.26969907407</v>
+        <v>46026.26789351852</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D29" s="2">
-        <v>46026.68943287037</v>
+        <v>46026.69395833334</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>247</v>
@@ -2233,7 +2233,7 @@
         <v>251</v>
       </c>
       <c r="G29" s="2">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H29" s="2">
         <v>0</v>
@@ -2250,13 +2250,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="2">
-        <v>46026.27083333334</v>
+        <v>46026.27777777778</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D30" s="2">
-        <v>46026.69851851852</v>
+        <v>46026.68976851852</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>247</v>
@@ -2265,7 +2265,7 @@
         <v>251</v>
       </c>
       <c r="G30" s="2">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H30" s="2">
         <v>0</v>
@@ -2282,22 +2282,18 @@
         <v>30</v>
       </c>
       <c r="B31" s="2">
-        <v>46026.43484953704</v>
+        <v>46026.95909722222</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="D31" s="2">
-        <v>46027.00256944444</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>247</v>
-      </c>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
       <c r="F31" s="2" t="s">
         <v>252</v>
       </c>
       <c r="G31" s="2">
-        <v>20</v>
+        <v>19.1</v>
       </c>
       <c r="H31" s="2">
         <v>0</v>
@@ -2314,13 +2310,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="2">
-        <v>46026.64583333334</v>
+        <v>46026.43458333334</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D32" s="2">
-        <v>46026.83052083333</v>
+        <v>46027.00340277778</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>247</v>
@@ -2329,7 +2325,7 @@
         <v>252</v>
       </c>
       <c r="G32" s="2">
-        <v>20</v>
+        <v>19.1</v>
       </c>
       <c r="H32" s="2">
         <v>0</v>
@@ -2346,22 +2342,18 @@
         <v>32</v>
       </c>
       <c r="B33" s="2">
-        <v>46026.63096064814</v>
+        <v>46026.96653935185</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="D33" s="2">
-        <v>46027.15564814815</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>247</v>
-      </c>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
       <c r="F33" s="2" t="s">
         <v>252</v>
       </c>
       <c r="G33" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H33" s="2">
         <v>0</v>
@@ -2378,25 +2370,21 @@
         <v>33</v>
       </c>
       <c r="B34" s="2">
-        <v>46026.45833333334</v>
+        <v>46026.4630787037</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="D34" s="2">
-        <v>46026.45833333334</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>244</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
       <c r="F34" s="2" t="s">
         <v>252</v>
       </c>
       <c r="G34" s="2">
-        <v>24</v>
+        <v>19.1</v>
       </c>
       <c r="H34" s="2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I34" s="2">
         <v>0</v>
@@ -2410,18 +2398,22 @@
         <v>34</v>
       </c>
       <c r="B35" s="2">
-        <v>46026.95178240741</v>
+        <v>46026.64583333334</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
+      <c r="D35" s="2">
+        <v>46026.83052083333</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>247</v>
+      </c>
       <c r="F35" s="2" t="s">
         <v>252</v>
       </c>
       <c r="G35" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H35" s="2">
         <v>0</v>
@@ -2438,18 +2430,22 @@
         <v>35</v>
       </c>
       <c r="B36" s="2">
-        <v>46026.95909722222</v>
+        <v>46026.63096064814</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
+      <c r="D36" s="2">
+        <v>46027.15564814815</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>247</v>
+      </c>
       <c r="F36" s="2" t="s">
         <v>252</v>
       </c>
       <c r="G36" s="2">
-        <v>19.1</v>
+        <v>23</v>
       </c>
       <c r="H36" s="2">
         <v>0</v>
@@ -2466,22 +2462,18 @@
         <v>36</v>
       </c>
       <c r="B37" s="2">
-        <v>46026.43458333334</v>
+        <v>46026.95178240741</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="D37" s="2">
-        <v>46027.00340277778</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>247</v>
-      </c>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
       <c r="F37" s="2" t="s">
         <v>252</v>
       </c>
       <c r="G37" s="2">
-        <v>19.1</v>
+        <v>23</v>
       </c>
       <c r="H37" s="2">
         <v>0</v>
@@ -2498,21 +2490,25 @@
         <v>37</v>
       </c>
       <c r="B38" s="2">
-        <v>46026.96653935185</v>
+        <v>46026.45833333334</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="D38" s="2">
+        <v>46026.45833333334</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>244</v>
+      </c>
       <c r="F38" s="2" t="s">
         <v>252</v>
       </c>
       <c r="G38" s="2">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H38" s="2">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I38" s="2">
         <v>0</v>
@@ -2526,18 +2522,22 @@
         <v>38</v>
       </c>
       <c r="B39" s="2">
-        <v>46026.4630787037</v>
+        <v>46026.43484953704</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
+      <c r="D39" s="2">
+        <v>46027.00256944444</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>247</v>
+      </c>
       <c r="F39" s="2" t="s">
         <v>252</v>
       </c>
       <c r="G39" s="2">
-        <v>19.1</v>
+        <v>20</v>
       </c>
       <c r="H39" s="2">
         <v>0</v>
@@ -2554,13 +2554,13 @@
         <v>39</v>
       </c>
       <c r="B40" s="2">
-        <v>46026.31253472222</v>
+        <v>46026.7297337963</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D40" s="2">
-        <v>46026.74887731481</v>
+        <v>46026.72975694444</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>247</v>
@@ -2569,7 +2569,7 @@
         <v>253</v>
       </c>
       <c r="G40" s="2">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H40" s="2">
         <v>0</v>
@@ -2586,13 +2586,13 @@
         <v>40</v>
       </c>
       <c r="B41" s="2">
-        <v>46026.31717592593</v>
+        <v>46026.30787037037</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D41" s="2">
-        <v>46026.74826388889</v>
+        <v>46026.72944444444</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>247</v>
@@ -2601,7 +2601,7 @@
         <v>253</v>
       </c>
       <c r="G41" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H41" s="2">
         <v>0</v>
@@ -2618,13 +2618,13 @@
         <v>41</v>
       </c>
       <c r="B42" s="2">
-        <v>46026.7297337963</v>
+        <v>46026.31717592593</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D42" s="2">
-        <v>46026.72975694444</v>
+        <v>46026.74826388889</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>247</v>
@@ -2633,7 +2633,7 @@
         <v>253</v>
       </c>
       <c r="G42" s="2">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H42" s="2">
         <v>0</v>
@@ -2647,25 +2647,25 @@
     </row>
     <row r="43" spans="1:10">
       <c r="A43" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B43" s="2">
-        <v>46026.32842592592</v>
+        <v>46026.31253472222</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D43" s="2">
-        <v>46026.7296875</v>
+        <v>46026.74887731481</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>253</v>
       </c>
       <c r="G43" s="2">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="H43" s="2">
         <v>0</v>
@@ -2679,19 +2679,19 @@
     </row>
     <row r="44" spans="1:10">
       <c r="A44" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B44" s="2">
-        <v>46026.30787037037</v>
+        <v>46026.32842592592</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D44" s="2">
-        <v>46026.72944444444</v>
+        <v>46026.7296875</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>253</v>
@@ -2714,13 +2714,13 @@
         <v>43</v>
       </c>
       <c r="B45" s="2">
-        <v>46026.00179398148</v>
+        <v>46026.45886574074</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D45" s="2">
-        <v>46026.44873842593</v>
+        <v>46026.97909722223</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>247</v>
@@ -2729,7 +2729,7 @@
         <v>254</v>
       </c>
       <c r="G45" s="2">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="H45" s="2">
         <v>0</v>
@@ -2746,22 +2746,18 @@
         <v>44</v>
       </c>
       <c r="B46" s="2">
-        <v>46026.64627314815</v>
+        <v>46026.46697916667</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="D46" s="2">
-        <v>46027.00524305556</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>247</v>
-      </c>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
       <c r="F46" s="2" t="s">
         <v>254</v>
       </c>
       <c r="G46" s="2">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H46" s="2">
         <v>0</v>
@@ -2778,13 +2774,13 @@
         <v>45</v>
       </c>
       <c r="B47" s="2">
-        <v>46026.45886574074</v>
+        <v>46026.00179398148</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D47" s="2">
-        <v>46026.97909722223</v>
+        <v>46026.44873842593</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>247</v>
@@ -2793,7 +2789,7 @@
         <v>254</v>
       </c>
       <c r="G47" s="2">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="H47" s="2">
         <v>0</v>
@@ -2810,18 +2806,22 @@
         <v>46</v>
       </c>
       <c r="B48" s="2">
-        <v>46026.46697916667</v>
+        <v>46026.64627314815</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
+      <c r="D48" s="2">
+        <v>46027.00524305556</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>247</v>
+      </c>
       <c r="F48" s="2" t="s">
         <v>254</v>
       </c>
       <c r="G48" s="2">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H48" s="2">
         <v>0</v>
@@ -2870,18 +2870,22 @@
         <v>48</v>
       </c>
       <c r="B50" s="2">
-        <v>46026.22821759259</v>
+        <v>46026.29123842593</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
+      <c r="D50" s="2">
+        <v>46026.50206018519</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>248</v>
+      </c>
       <c r="F50" s="2" t="s">
         <v>255</v>
       </c>
       <c r="G50" s="2">
-        <v>30</v>
+        <v>33.14</v>
       </c>
       <c r="H50" s="2">
         <v>0</v>
@@ -2898,13 +2902,13 @@
         <v>49</v>
       </c>
       <c r="B51" s="2">
-        <v>46026.52152777778</v>
+        <v>46026.22821759259</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D51" s="2">
-        <v>46026.72953703703</v>
+        <v>46026.64583333334</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>247</v>
@@ -2913,7 +2917,7 @@
         <v>255</v>
       </c>
       <c r="G51" s="2">
-        <v>26.78</v>
+        <v>30</v>
       </c>
       <c r="H51" s="2">
         <v>0</v>
@@ -2930,13 +2934,13 @@
         <v>50</v>
       </c>
       <c r="B52" s="2">
-        <v>46026.29123842593</v>
+        <v>46026.29340277778</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D52" s="2">
-        <v>46026.50206018519</v>
+        <v>46026.50195601852</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>248</v>
@@ -2945,7 +2949,7 @@
         <v>255</v>
       </c>
       <c r="G52" s="2">
-        <v>33.14</v>
+        <v>24</v>
       </c>
       <c r="H52" s="2">
         <v>0</v>
@@ -2962,13 +2966,13 @@
         <v>50</v>
       </c>
       <c r="B53" s="2">
-        <v>46026.52065972222</v>
+        <v>46026.52159722222</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>243</v>
       </c>
       <c r="D53" s="2">
-        <v>46026.72936342593</v>
+        <v>46026.72918981482</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>247</v>
@@ -2977,7 +2981,7 @@
         <v>255</v>
       </c>
       <c r="G53" s="2">
-        <v>33.14</v>
+        <v>24</v>
       </c>
       <c r="H53" s="2">
         <v>0</v>
@@ -2994,13 +2998,13 @@
         <v>51</v>
       </c>
       <c r="B54" s="2">
-        <v>46026.29340277778</v>
+        <v>46026.34697916666</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D54" s="2">
-        <v>46026.50195601852</v>
+        <v>46026.50349537037</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>248</v>
@@ -3009,7 +3013,7 @@
         <v>255</v>
       </c>
       <c r="G54" s="2">
-        <v>24</v>
+        <v>26.78</v>
       </c>
       <c r="H54" s="2">
         <v>0</v>
@@ -3023,16 +3027,16 @@
     </row>
     <row r="55" spans="1:10">
       <c r="A55" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B55" s="2">
-        <v>46026.52159722222</v>
+        <v>46026.52065972222</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>243</v>
       </c>
       <c r="D55" s="2">
-        <v>46026.72918981482</v>
+        <v>46026.72936342593</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>247</v>
@@ -3041,7 +3045,7 @@
         <v>255</v>
       </c>
       <c r="G55" s="2">
-        <v>24</v>
+        <v>33.14</v>
       </c>
       <c r="H55" s="2">
         <v>0</v>
@@ -3055,19 +3059,19 @@
     </row>
     <row r="56" spans="1:10">
       <c r="A56" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B56" s="2">
-        <v>46026.34697916666</v>
+        <v>46026.52152777778</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D56" s="2">
-        <v>46026.50349537037</v>
+        <v>46026.72953703703</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>255</v>
@@ -3090,13 +3094,13 @@
         <v>52</v>
       </c>
       <c r="B57" s="2">
-        <v>46026.49534722222</v>
+        <v>46026.31313657408</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D57" s="2">
-        <v>46026.71655092593</v>
+        <v>46026.7067824074</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>247</v>
@@ -3105,7 +3109,7 @@
         <v>256</v>
       </c>
       <c r="G57" s="2">
-        <v>24</v>
+        <v>19.85</v>
       </c>
       <c r="H57" s="2">
         <v>0</v>
@@ -3122,13 +3126,13 @@
         <v>53</v>
       </c>
       <c r="B58" s="2">
-        <v>46026.31164351852</v>
+        <v>46026.31180555555</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D58" s="2">
-        <v>46026.7149074074</v>
+        <v>46026.71445601852</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>247</v>
@@ -3137,7 +3141,7 @@
         <v>256</v>
       </c>
       <c r="G58" s="2">
-        <v>19.03</v>
+        <v>19.85</v>
       </c>
       <c r="H58" s="2">
         <v>0</v>
@@ -3154,13 +3158,13 @@
         <v>54</v>
       </c>
       <c r="B59" s="2">
-        <v>46026.31208333333</v>
+        <v>46026.32366898148</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D59" s="2">
-        <v>46026.71616898148</v>
+        <v>46026.715625</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>247</v>
@@ -3169,7 +3173,7 @@
         <v>256</v>
       </c>
       <c r="G59" s="2">
-        <v>21.35</v>
+        <v>19.85</v>
       </c>
       <c r="H59" s="2">
         <v>0</v>
@@ -3186,13 +3190,13 @@
         <v>55</v>
       </c>
       <c r="B60" s="2">
-        <v>46026.31149305555</v>
+        <v>46026.49534722222</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D60" s="2">
-        <v>46026.7146875</v>
+        <v>46026.71655092593</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>247</v>
@@ -3201,7 +3205,7 @@
         <v>256</v>
       </c>
       <c r="G60" s="2">
-        <v>21.72</v>
+        <v>24</v>
       </c>
       <c r="H60" s="2">
         <v>0</v>
@@ -3218,13 +3222,13 @@
         <v>56</v>
       </c>
       <c r="B61" s="2">
-        <v>46026.33035879629</v>
+        <v>46026.31136574074</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D61" s="2">
-        <v>46026.67427083333</v>
+        <v>46026.71678240741</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>247</v>
@@ -3233,7 +3237,7 @@
         <v>256</v>
       </c>
       <c r="G61" s="2">
-        <v>20</v>
+        <v>24.08</v>
       </c>
       <c r="H61" s="2">
         <v>0</v>
@@ -3282,13 +3286,13 @@
         <v>58</v>
       </c>
       <c r="B63" s="2">
-        <v>46026.31136574074</v>
+        <v>46026.31164351852</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D63" s="2">
-        <v>46026.71678240741</v>
+        <v>46026.7149074074</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>247</v>
@@ -3297,7 +3301,7 @@
         <v>256</v>
       </c>
       <c r="G63" s="2">
-        <v>24.08</v>
+        <v>19.03</v>
       </c>
       <c r="H63" s="2">
         <v>0</v>
@@ -3314,13 +3318,13 @@
         <v>59</v>
       </c>
       <c r="B64" s="2">
-        <v>46026.31195601852</v>
+        <v>46026.31221064815</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D64" s="2">
-        <v>46026.71511574074</v>
+        <v>46026.7172337963</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>247</v>
@@ -3346,13 +3350,13 @@
         <v>60</v>
       </c>
       <c r="B65" s="2">
-        <v>46026.31328703704</v>
+        <v>46026.33035879629</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D65" s="2">
-        <v>46026.71635416667</v>
+        <v>46026.67427083333</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>247</v>
@@ -3361,7 +3365,7 @@
         <v>256</v>
       </c>
       <c r="G65" s="2">
-        <v>20.35</v>
+        <v>20</v>
       </c>
       <c r="H65" s="2">
         <v>0</v>
@@ -3378,13 +3382,13 @@
         <v>61</v>
       </c>
       <c r="B66" s="2">
-        <v>46026.31648148148</v>
+        <v>46026.3109375</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D66" s="2">
-        <v>46026.7153587963</v>
+        <v>46026.71527777778</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>247</v>
@@ -3393,7 +3397,7 @@
         <v>256</v>
       </c>
       <c r="G66" s="2">
-        <v>26.83</v>
+        <v>19.85</v>
       </c>
       <c r="H66" s="2">
         <v>0</v>
@@ -3410,13 +3414,13 @@
         <v>62</v>
       </c>
       <c r="B67" s="2">
-        <v>46026.31313657408</v>
+        <v>46026.31671296297</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D67" s="2">
-        <v>46026.7067824074</v>
+        <v>46026.71203703704</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>247</v>
@@ -3425,7 +3429,7 @@
         <v>256</v>
       </c>
       <c r="G67" s="2">
-        <v>19.85</v>
+        <v>18.03</v>
       </c>
       <c r="H67" s="2">
         <v>0</v>
@@ -3442,13 +3446,13 @@
         <v>63</v>
       </c>
       <c r="B68" s="2">
-        <v>46026.31180555555</v>
+        <v>46026.31070601852</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D68" s="2">
-        <v>46026.71445601852</v>
+        <v>46026.71653935185</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>247</v>
@@ -3474,13 +3478,13 @@
         <v>64</v>
       </c>
       <c r="B69" s="2">
-        <v>46026.31108796296</v>
+        <v>46026.3181712963</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D69" s="2">
-        <v>46026.71180555555</v>
+        <v>46026.71256944445</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>247</v>
@@ -3489,7 +3493,7 @@
         <v>256</v>
       </c>
       <c r="G69" s="2">
-        <v>27.58</v>
+        <v>22.58</v>
       </c>
       <c r="H69" s="2">
         <v>0</v>
@@ -3506,13 +3510,13 @@
         <v>65</v>
       </c>
       <c r="B70" s="2">
-        <v>46026.32366898148</v>
+        <v>46026.31648148148</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D70" s="2">
-        <v>46026.715625</v>
+        <v>46026.7153587963</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>247</v>
@@ -3521,7 +3525,7 @@
         <v>256</v>
       </c>
       <c r="G70" s="2">
-        <v>19.85</v>
+        <v>26.83</v>
       </c>
       <c r="H70" s="2">
         <v>0</v>
@@ -3538,13 +3542,13 @@
         <v>66</v>
       </c>
       <c r="B71" s="2">
-        <v>46026.31221064815</v>
+        <v>46026.31328703704</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D71" s="2">
-        <v>46026.7172337963</v>
+        <v>46026.71635416667</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>247</v>
@@ -3553,7 +3557,7 @@
         <v>256</v>
       </c>
       <c r="G71" s="2">
-        <v>19.85</v>
+        <v>20.35</v>
       </c>
       <c r="H71" s="2">
         <v>0</v>
@@ -3570,13 +3574,13 @@
         <v>67</v>
       </c>
       <c r="B72" s="2">
-        <v>46026.31671296297</v>
+        <v>46026.31149305555</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D72" s="2">
-        <v>46026.71203703704</v>
+        <v>46026.7146875</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>247</v>
@@ -3585,7 +3589,7 @@
         <v>256</v>
       </c>
       <c r="G72" s="2">
-        <v>18.03</v>
+        <v>21.72</v>
       </c>
       <c r="H72" s="2">
         <v>0</v>
@@ -3602,13 +3606,13 @@
         <v>68</v>
       </c>
       <c r="B73" s="2">
-        <v>46026.3181712963</v>
+        <v>46026.31208333333</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D73" s="2">
-        <v>46026.71256944445</v>
+        <v>46026.71616898148</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>247</v>
@@ -3617,7 +3621,7 @@
         <v>256</v>
       </c>
       <c r="G73" s="2">
-        <v>22.58</v>
+        <v>21.35</v>
       </c>
       <c r="H73" s="2">
         <v>0</v>
@@ -3634,13 +3638,13 @@
         <v>69</v>
       </c>
       <c r="B74" s="2">
-        <v>46026.31070601852</v>
+        <v>46026.31108796296</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D74" s="2">
-        <v>46026.71653935185</v>
+        <v>46026.71180555555</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>247</v>
@@ -3649,7 +3653,7 @@
         <v>256</v>
       </c>
       <c r="G74" s="2">
-        <v>19.85</v>
+        <v>27.58</v>
       </c>
       <c r="H74" s="2">
         <v>0</v>
@@ -3666,13 +3670,17 @@
         <v>70</v>
       </c>
       <c r="B75" s="2">
-        <v>46026.3109375</v>
+        <v>46026.31195601852</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="D75" s="2"/>
-      <c r="E75" s="2"/>
+      <c r="D75" s="2">
+        <v>46026.71511574074</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>247</v>
+      </c>
       <c r="F75" s="2" t="s">
         <v>256</v>
       </c>
@@ -3694,22 +3702,22 @@
         <v>71</v>
       </c>
       <c r="B76" s="2">
-        <v>46026.575625</v>
+        <v>46026.32942129629</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D76" s="2">
-        <v>46026.70174768518</v>
+        <v>46026.54353009259</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>257</v>
       </c>
       <c r="G76" s="2">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="H76" s="2">
         <v>0</v>
@@ -3723,16 +3731,16 @@
     </row>
     <row r="77" spans="1:10">
       <c r="A77" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B77" s="2">
-        <v>46026.50121527778</v>
+        <v>46026.63901620371</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>243</v>
       </c>
       <c r="D77" s="2">
-        <v>46026.7071875</v>
+        <v>46026.71149305555</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>247</v>
@@ -3741,7 +3749,7 @@
         <v>257</v>
       </c>
       <c r="G77" s="2">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="H77" s="2">
         <v>0</v>
@@ -3755,19 +3763,19 @@
     </row>
     <row r="78" spans="1:10">
       <c r="A78" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B78" s="2">
-        <v>46026.33333333334</v>
+        <v>46026.33168981481</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D78" s="2">
-        <v>46026.33333333334</v>
+        <v>46026.50408564815</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>257</v>
@@ -3776,7 +3784,7 @@
         <v>18</v>
       </c>
       <c r="H78" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I78" s="2">
         <v>0</v>
@@ -3787,16 +3795,16 @@
     </row>
     <row r="79" spans="1:10">
       <c r="A79" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B79" s="2">
-        <v>46026.33280092593</v>
+        <v>46026.33072916666</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D79" s="2">
-        <v>46026.63828703704</v>
+        <v>46026.51096064815</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>248</v>
@@ -3805,7 +3813,7 @@
         <v>257</v>
       </c>
       <c r="G79" s="2">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="H79" s="2">
         <v>0</v>
@@ -3819,16 +3827,16 @@
     </row>
     <row r="80" spans="1:10">
       <c r="A80" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B80" s="2">
-        <v>46026.6796875</v>
+        <v>46026.55765046296</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>243</v>
       </c>
       <c r="D80" s="2">
-        <v>46026.75032407408</v>
+        <v>46027.33128472222</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>247</v>
@@ -3837,7 +3845,7 @@
         <v>257</v>
       </c>
       <c r="G80" s="2">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="H80" s="2">
         <v>0</v>
@@ -3851,7 +3859,7 @@
     </row>
     <row r="81" spans="1:10">
       <c r="A81" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B81" s="2">
         <v>46026.33175925926</v>
@@ -3883,25 +3891,25 @@
     </row>
     <row r="82" spans="1:10">
       <c r="A82" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B82" s="2">
-        <v>46026.31379629629</v>
+        <v>46026.32606481481</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D82" s="2">
-        <v>46026.46581018518</v>
+        <v>46026.70865740741</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>257</v>
       </c>
       <c r="G82" s="2">
-        <v>18</v>
+        <v>24.72</v>
       </c>
       <c r="H82" s="2">
         <v>0</v>
@@ -3915,16 +3923,16 @@
     </row>
     <row r="83" spans="1:10">
       <c r="A83" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B83" s="2">
-        <v>46026.52162037037</v>
+        <v>46026.52856481481</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>243</v>
       </c>
       <c r="D83" s="2">
-        <v>46026.69010416666</v>
+        <v>46026.69099537037</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>247</v>
@@ -3947,16 +3955,16 @@
     </row>
     <row r="84" spans="1:10">
       <c r="A84" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B84" s="2">
-        <v>46026.33145833333</v>
+        <v>46026.34733796296</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D84" s="2">
-        <v>46026.583125</v>
+        <v>46026.46030092592</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>248</v>
@@ -3979,16 +3987,16 @@
     </row>
     <row r="85" spans="1:10">
       <c r="A85" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B85" s="2">
-        <v>46026.52856481481</v>
+        <v>46026.50121527778</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>243</v>
       </c>
       <c r="D85" s="2">
-        <v>46026.69099537037</v>
+        <v>46026.7071875</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>247</v>
@@ -3997,7 +4005,7 @@
         <v>257</v>
       </c>
       <c r="G85" s="2">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="H85" s="2">
         <v>0</v>
@@ -4011,16 +4019,16 @@
     </row>
     <row r="86" spans="1:10">
       <c r="A86" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B86" s="2">
-        <v>46026.33168981481</v>
+        <v>46026.33199074074</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D86" s="2">
-        <v>46026.50408564815</v>
+        <v>46026.54211805556</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>248</v>
@@ -4029,7 +4037,7 @@
         <v>257</v>
       </c>
       <c r="G86" s="2">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="H86" s="2">
         <v>0</v>
@@ -4046,13 +4054,13 @@
         <v>78</v>
       </c>
       <c r="B87" s="2">
-        <v>46026.52846064815</v>
+        <v>46026.32821759259</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D87" s="2">
-        <v>46026.6890162037</v>
+        <v>46026.60233796296</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>247</v>
@@ -4061,7 +4069,7 @@
         <v>257</v>
       </c>
       <c r="G87" s="2">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="H87" s="2">
         <v>0</v>
@@ -4078,22 +4086,22 @@
         <v>79</v>
       </c>
       <c r="B88" s="2">
-        <v>46026.33072916666</v>
+        <v>46026.62453703704</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D88" s="2">
-        <v>46026.51096064815</v>
+        <v>46026.70679398148</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>257</v>
       </c>
       <c r="G88" s="2">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="H88" s="2">
         <v>0</v>
@@ -4107,16 +4115,16 @@
     </row>
     <row r="89" spans="1:10">
       <c r="A89" s="2" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B89" s="2">
-        <v>46026.34733796296</v>
+        <v>46026.32611111111</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D89" s="2">
-        <v>46026.46030092592</v>
+        <v>46026.50579861111</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>248</v>
@@ -4125,7 +4133,7 @@
         <v>257</v>
       </c>
       <c r="G89" s="2">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="H89" s="2">
         <v>0</v>
@@ -4139,25 +4147,25 @@
     </row>
     <row r="90" spans="1:10">
       <c r="A90" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B90" s="2">
-        <v>46026.32725694445</v>
+        <v>46026.575625</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D90" s="2">
-        <v>46026.53752314814</v>
+        <v>46026.70174768518</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>257</v>
       </c>
       <c r="G90" s="2">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="H90" s="2">
         <v>0</v>
@@ -4174,13 +4182,13 @@
         <v>81</v>
       </c>
       <c r="B91" s="2">
-        <v>46026.50438657407</v>
+        <v>46026.52162037037</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>243</v>
       </c>
       <c r="D91" s="2">
-        <v>46026.71108796296</v>
+        <v>46026.69010416666</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>247</v>
@@ -4189,7 +4197,7 @@
         <v>257</v>
       </c>
       <c r="G91" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H91" s="2">
         <v>0</v>
@@ -4203,16 +4211,16 @@
     </row>
     <row r="92" spans="1:10">
       <c r="A92" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B92" s="2">
-        <v>46026.32625</v>
+        <v>46026.31379629629</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D92" s="2">
-        <v>46026.5083912037</v>
+        <v>46026.46581018518</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>248</v>
@@ -4221,7 +4229,7 @@
         <v>257</v>
       </c>
       <c r="G92" s="2">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="H92" s="2">
         <v>0</v>
@@ -4235,25 +4243,25 @@
     </row>
     <row r="93" spans="1:10">
       <c r="A93" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B93" s="2">
-        <v>46026.32611111111</v>
+        <v>46026.58486111111</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D93" s="2">
-        <v>46026.50579861111</v>
+        <v>46026.70459490741</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>257</v>
       </c>
       <c r="G93" s="2">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="H93" s="2">
         <v>0</v>
@@ -4267,21 +4275,25 @@
     </row>
     <row r="94" spans="1:10">
       <c r="A94" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B94" s="2">
-        <v>46026.55765046296</v>
+        <v>46026.33107638889</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="D94" s="2"/>
-      <c r="E94" s="2"/>
+        <v>242</v>
+      </c>
+      <c r="D94" s="2">
+        <v>46026.54313657407</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>248</v>
+      </c>
       <c r="F94" s="2" t="s">
         <v>257</v>
       </c>
       <c r="G94" s="2">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="H94" s="2">
         <v>0</v>
@@ -4295,16 +4307,16 @@
     </row>
     <row r="95" spans="1:10">
       <c r="A95" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B95" s="2">
-        <v>46026.5575462963</v>
+        <v>46026.52410879629</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>243</v>
       </c>
       <c r="D95" s="2">
-        <v>46026.71324074074</v>
+        <v>46026.71173611111</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>247</v>
@@ -4313,7 +4325,7 @@
         <v>257</v>
       </c>
       <c r="G95" s="2">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="H95" s="2">
         <v>0</v>
@@ -4327,25 +4339,25 @@
     </row>
     <row r="96" spans="1:10">
       <c r="A96" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B96" s="2">
-        <v>46026.32871527778</v>
+        <v>46026.3309375</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D96" s="2">
-        <v>46026.69417824074</v>
+        <v>46026.46619212963</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>257</v>
       </c>
       <c r="G96" s="2">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H96" s="2">
         <v>0</v>
@@ -4359,19 +4371,19 @@
     </row>
     <row r="97" spans="1:10">
       <c r="A97" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B97" s="2">
-        <v>46026.32954861111</v>
+        <v>46026.32853009259</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D97" s="2">
-        <v>46026.45532407407</v>
+        <v>46026.69114583333</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>257</v>
@@ -4391,16 +4403,16 @@
     </row>
     <row r="98" spans="1:10">
       <c r="A98" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B98" s="2">
-        <v>46026.55025462963</v>
+        <v>46026.50282407407</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>243</v>
       </c>
       <c r="D98" s="2">
-        <v>46026.75112268519</v>
+        <v>46026.65922453703</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>247</v>
@@ -4409,7 +4421,7 @@
         <v>257</v>
       </c>
       <c r="G98" s="2">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="H98" s="2">
         <v>0</v>
@@ -4423,25 +4435,25 @@
     </row>
     <row r="99" spans="1:10">
       <c r="A99" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B99" s="2">
-        <v>46026.5044212963</v>
+        <v>46026.33543981481</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D99" s="2">
-        <v>46026.70841435185</v>
+        <v>46026.45908564814</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>257</v>
       </c>
       <c r="G99" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H99" s="2">
         <v>0</v>
@@ -4455,16 +4467,16 @@
     </row>
     <row r="100" spans="1:10">
       <c r="A100" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B100" s="2">
-        <v>46026.63777777777</v>
+        <v>46026.50745370371</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>243</v>
       </c>
       <c r="D100" s="2">
-        <v>46026.71087962963</v>
+        <v>46026.70679398148</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>247</v>
@@ -4487,16 +4499,16 @@
     </row>
     <row r="101" spans="1:10">
       <c r="A101" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B101" s="2">
-        <v>46026.33003472222</v>
+        <v>46026.33157407407</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D101" s="2">
-        <v>46026.53590277778</v>
+        <v>46026.46230324074</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>248</v>
@@ -4505,7 +4517,7 @@
         <v>257</v>
       </c>
       <c r="G101" s="2">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="H101" s="2">
         <v>0</v>
@@ -4519,19 +4531,19 @@
     </row>
     <row r="102" spans="1:10">
       <c r="A102" s="2" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="B102" s="2">
-        <v>46026.33199074074</v>
+        <v>46026.55025462963</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D102" s="2">
-        <v>46026.54211805556</v>
+        <v>46026.75112268519</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>257</v>
@@ -4551,19 +4563,19 @@
     </row>
     <row r="103" spans="1:10">
       <c r="A103" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B103" s="2">
-        <v>46026.53789351852</v>
+        <v>46026.32625</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D103" s="2">
-        <v>46026.71121527778</v>
+        <v>46026.5083912037</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>257</v>
@@ -4583,16 +4595,16 @@
     </row>
     <row r="104" spans="1:10">
       <c r="A104" s="2" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="B104" s="2">
-        <v>46026.32287037037</v>
+        <v>46026.33145833333</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D104" s="2">
-        <v>46026.49961805555</v>
+        <v>46026.583125</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>248</v>
@@ -4615,19 +4627,19 @@
     </row>
     <row r="105" spans="1:10">
       <c r="A105" s="2" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="B105" s="2">
-        <v>46026.63924768518</v>
+        <v>46026.33222222222</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D105" s="2">
-        <v>46026.70623842593</v>
+        <v>46026.45965277778</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>257</v>
@@ -4647,19 +4659,19 @@
     </row>
     <row r="106" spans="1:10">
       <c r="A106" s="2" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="B106" s="2">
-        <v>46026.33186342593</v>
+        <v>46026.52846064815</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D106" s="2">
-        <v>46026.54047453704</v>
+        <v>46026.6890162037</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>257</v>
@@ -4679,28 +4691,28 @@
     </row>
     <row r="107" spans="1:10">
       <c r="A107" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B107" s="2">
-        <v>46026.57640046296</v>
+        <v>46026.33333333334</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D107" s="2">
-        <v>46026.70914351852</v>
+        <v>46026.33333333334</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>257</v>
       </c>
       <c r="G107" s="2">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="H107" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I107" s="2">
         <v>0</v>
@@ -4714,13 +4726,13 @@
         <v>90</v>
       </c>
       <c r="B108" s="2">
-        <v>46026.33157407407</v>
+        <v>46026.33212962963</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D108" s="2">
-        <v>46026.46230324074</v>
+        <v>46026.56300925926</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>248</v>
@@ -4729,7 +4741,7 @@
         <v>257</v>
       </c>
       <c r="G108" s="2">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="H108" s="2">
         <v>0</v>
@@ -4743,25 +4755,25 @@
     </row>
     <row r="109" spans="1:10">
       <c r="A109" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B109" s="2">
-        <v>46026.33543981481</v>
+        <v>46026.60165509259</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D109" s="2">
-        <v>46026.45908564814</v>
+        <v>46026.75134259259</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>257</v>
       </c>
       <c r="G109" s="2">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="H109" s="2">
         <v>0</v>
@@ -4775,25 +4787,25 @@
     </row>
     <row r="110" spans="1:10">
       <c r="A110" s="2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B110" s="2">
-        <v>46026.33577546296</v>
+        <v>46026.50297453703</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D110" s="2">
-        <v>46026.46725694444</v>
+        <v>46026.70283564815</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>257</v>
       </c>
       <c r="G110" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H110" s="2">
         <v>0</v>
@@ -4807,16 +4819,16 @@
     </row>
     <row r="111" spans="1:10">
       <c r="A111" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B111" s="2">
-        <v>46026.63901620371</v>
+        <v>46026.6084375</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>243</v>
       </c>
       <c r="D111" s="2">
-        <v>46026.71149305555</v>
+        <v>46026.71065972222</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>247</v>
@@ -4825,7 +4837,7 @@
         <v>257</v>
       </c>
       <c r="G111" s="2">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="H111" s="2">
         <v>0</v>
@@ -4842,22 +4854,22 @@
         <v>92</v>
       </c>
       <c r="B112" s="2">
-        <v>46026.32942129629</v>
+        <v>46026.50438657407</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D112" s="2">
-        <v>46026.54353009259</v>
+        <v>46026.71108796296</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>257</v>
       </c>
       <c r="G112" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H112" s="2">
         <v>0</v>
@@ -4871,25 +4883,25 @@
     </row>
     <row r="113" spans="1:10">
       <c r="A113" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B113" s="2">
-        <v>46026.32606481481</v>
+        <v>46026.33577546296</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D113" s="2">
-        <v>46026.70865740741</v>
+        <v>46026.46725694444</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F113" s="2" t="s">
         <v>257</v>
       </c>
       <c r="G113" s="2">
-        <v>24.72</v>
+        <v>15</v>
       </c>
       <c r="H113" s="2">
         <v>0</v>
@@ -4903,16 +4915,16 @@
     </row>
     <row r="114" spans="1:10">
       <c r="A114" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B114" s="2">
-        <v>46026.58486111111</v>
+        <v>46026.5827662037</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>243</v>
       </c>
       <c r="D114" s="2">
-        <v>46026.70459490741</v>
+        <v>46026.70587962963</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>247</v>
@@ -4935,16 +4947,16 @@
     </row>
     <row r="115" spans="1:10">
       <c r="A115" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B115" s="2">
-        <v>46026.33107638889</v>
+        <v>46026.33267361111</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D115" s="2">
-        <v>46026.54313657407</v>
+        <v>46026.54188657407</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>248</v>
@@ -4967,16 +4979,16 @@
     </row>
     <row r="116" spans="1:10">
       <c r="A116" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B116" s="2">
-        <v>46026.50745370371</v>
+        <v>46026.53789351852</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>243</v>
       </c>
       <c r="D116" s="2">
-        <v>46026.70679398148</v>
+        <v>46026.71121527778</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>247</v>
@@ -4985,7 +4997,7 @@
         <v>257</v>
       </c>
       <c r="G116" s="2">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="H116" s="2">
         <v>0</v>
@@ -4999,25 +5011,25 @@
     </row>
     <row r="117" spans="1:10">
       <c r="A117" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B117" s="2">
-        <v>46026.52410879629</v>
+        <v>46026.32287037037</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D117" s="2">
-        <v>46026.71173611111</v>
+        <v>46026.49961805555</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F117" s="2" t="s">
         <v>257</v>
       </c>
       <c r="G117" s="2">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="H117" s="2">
         <v>0</v>
@@ -5031,16 +5043,16 @@
     </row>
     <row r="118" spans="1:10">
       <c r="A118" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B118" s="2">
-        <v>46026.52598379629</v>
+        <v>46026.63924768518</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D118" s="2">
-        <v>46026.71452546296</v>
+        <v>46026.70623842593</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>247</v>
@@ -5049,7 +5061,7 @@
         <v>257</v>
       </c>
       <c r="G118" s="2">
-        <v>24.72</v>
+        <v>18</v>
       </c>
       <c r="H118" s="2">
         <v>0</v>
@@ -5063,25 +5075,25 @@
     </row>
     <row r="119" spans="1:10">
       <c r="A119" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B119" s="2">
-        <v>46026.32019675926</v>
+        <v>46026.32725694445</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D119" s="2">
-        <v>46026.46333333333</v>
+        <v>46026.53752314814</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>257</v>
       </c>
       <c r="G119" s="2">
-        <v>24.72</v>
+        <v>18</v>
       </c>
       <c r="H119" s="2">
         <v>0</v>
@@ -5095,19 +5107,19 @@
     </row>
     <row r="120" spans="1:10">
       <c r="A120" s="2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B120" s="2">
-        <v>46026.5827662037</v>
+        <v>46026.32653935185</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D120" s="2">
-        <v>46026.70587962963</v>
+        <v>46026.56695601852</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>257</v>
@@ -5127,16 +5139,16 @@
     </row>
     <row r="121" spans="1:10">
       <c r="A121" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B121" s="2">
-        <v>46026.33267361111</v>
+        <v>46026.33003472222</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D121" s="2">
-        <v>46026.54188657407</v>
+        <v>46026.53590277778</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>248</v>
@@ -5159,16 +5171,16 @@
     </row>
     <row r="122" spans="1:10">
       <c r="A122" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B122" s="2">
-        <v>46026.32853009259</v>
+        <v>46026.57640046296</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D122" s="2">
-        <v>46026.69114583333</v>
+        <v>46026.70914351852</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>247</v>
@@ -5177,7 +5189,7 @@
         <v>257</v>
       </c>
       <c r="G122" s="2">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="H122" s="2">
         <v>0</v>
@@ -5191,25 +5203,25 @@
     </row>
     <row r="123" spans="1:10">
       <c r="A123" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B123" s="2">
-        <v>46026.50282407407</v>
+        <v>46026.33280092593</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D123" s="2">
-        <v>46026.65922453703</v>
+        <v>46026.63828703704</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F123" s="2" t="s">
         <v>257</v>
       </c>
       <c r="G123" s="2">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="H123" s="2">
         <v>0</v>
@@ -5223,25 +5235,25 @@
     </row>
     <row r="124" spans="1:10">
       <c r="A124" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B124" s="2">
-        <v>46026.3309375</v>
+        <v>46026.6796875</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D124" s="2">
-        <v>46026.46619212963</v>
+        <v>46026.75032407408</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>257</v>
       </c>
       <c r="G124" s="2">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="H124" s="2">
         <v>0</v>
@@ -5255,16 +5267,16 @@
     </row>
     <row r="125" spans="1:10">
       <c r="A125" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B125" s="2">
-        <v>46026.32821759259</v>
+        <v>46026.32019675926</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D125" s="2">
-        <v>46026.60233796296</v>
+        <v>46026.46333333333</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>247</v>
@@ -5273,7 +5285,7 @@
         <v>257</v>
       </c>
       <c r="G125" s="2">
-        <v>17.5</v>
+        <v>24.72</v>
       </c>
       <c r="H125" s="2">
         <v>0</v>
@@ -5287,7 +5299,7 @@
     </row>
     <row r="126" spans="1:10">
       <c r="A126" s="2" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="B126" s="2">
         <v>46026.33086805556</v>
@@ -5319,16 +5331,16 @@
     </row>
     <row r="127" spans="1:10">
       <c r="A127" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B127" s="2">
-        <v>46026.50297453703</v>
+        <v>46026.52598379629</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D127" s="2">
-        <v>46026.70283564815</v>
+        <v>46026.71452546296</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>247</v>
@@ -5337,7 +5349,7 @@
         <v>257</v>
       </c>
       <c r="G127" s="2">
-        <v>18</v>
+        <v>24.72</v>
       </c>
       <c r="H127" s="2">
         <v>0</v>
@@ -5351,25 +5363,25 @@
     </row>
     <row r="128" spans="1:10">
       <c r="A128" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B128" s="2">
-        <v>46026.33212962963</v>
+        <v>46026.32871527778</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D128" s="2">
-        <v>46026.56300925926</v>
+        <v>46026.69417824074</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F128" s="2" t="s">
         <v>257</v>
       </c>
       <c r="G128" s="2">
-        <v>17.5</v>
+        <v>24</v>
       </c>
       <c r="H128" s="2">
         <v>0</v>
@@ -5386,13 +5398,13 @@
         <v>101</v>
       </c>
       <c r="B129" s="2">
-        <v>46026.60165509259</v>
+        <v>46026.63777777777</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>243</v>
       </c>
       <c r="D129" s="2">
-        <v>46026.75134259259</v>
+        <v>46026.71087962963</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>247</v>
@@ -5401,7 +5413,7 @@
         <v>257</v>
       </c>
       <c r="G129" s="2">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="H129" s="2">
         <v>0</v>
@@ -5415,19 +5427,19 @@
     </row>
     <row r="130" spans="1:10">
       <c r="A130" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B130" s="2">
-        <v>46026.32653935185</v>
+        <v>46026.5575462963</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D130" s="2">
-        <v>46026.56695601852</v>
+        <v>46026.71324074074</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F130" s="2" t="s">
         <v>257</v>
@@ -5450,13 +5462,13 @@
         <v>102</v>
       </c>
       <c r="B131" s="2">
-        <v>46026.6084375</v>
+        <v>46026.5044212963</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>243</v>
       </c>
       <c r="D131" s="2">
-        <v>46026.71065972222</v>
+        <v>46026.70841435185</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>247</v>
@@ -5465,7 +5477,7 @@
         <v>257</v>
       </c>
       <c r="G131" s="2">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="H131" s="2">
         <v>0</v>
@@ -5479,25 +5491,25 @@
     </row>
     <row r="132" spans="1:10">
       <c r="A132" s="2" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="B132" s="2">
-        <v>46026.62453703704</v>
+        <v>46026.32954861111</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D132" s="2">
-        <v>46026.70679398148</v>
+        <v>46026.45532407407</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F132" s="2" t="s">
         <v>257</v>
       </c>
       <c r="G132" s="2">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="H132" s="2">
         <v>0</v>
@@ -5511,16 +5523,16 @@
     </row>
     <row r="133" spans="1:10">
       <c r="A133" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B133" s="2">
-        <v>46026.33222222222</v>
+        <v>46026.33186342593</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D133" s="2">
-        <v>46026.45965277778</v>
+        <v>46026.54047453704</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>248</v>
@@ -5561,13 +5573,13 @@
         <v>258</v>
       </c>
       <c r="G134" s="2">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="H134" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I134" s="2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J134" s="2" t="s">
         <v>290</v>
@@ -5575,7 +5587,7 @@
     </row>
     <row r="135" spans="1:10">
       <c r="A135" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B135" s="2">
         <v>46026</v>
@@ -5593,13 +5605,13 @@
         <v>258</v>
       </c>
       <c r="G135" s="2">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="H135" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I135" s="2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J135" s="2" t="s">
         <v>290</v>
@@ -5625,10 +5637,10 @@
         <v>258</v>
       </c>
       <c r="G136" s="2">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="H136" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I136" s="2">
         <v>0</v>
@@ -5657,7 +5669,7 @@
         <v>258</v>
       </c>
       <c r="G137" s="2">
-        <v>17.64</v>
+        <v>16</v>
       </c>
       <c r="H137" s="2">
         <v>6</v>
@@ -5689,10 +5701,10 @@
         <v>258</v>
       </c>
       <c r="G138" s="2">
-        <v>19.24</v>
+        <v>17.64</v>
       </c>
       <c r="H138" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I138" s="2">
         <v>0</v>
@@ -5721,10 +5733,10 @@
         <v>258</v>
       </c>
       <c r="G139" s="2">
-        <v>19.15</v>
+        <v>15.5</v>
       </c>
       <c r="H139" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I139" s="2">
         <v>0</v>
@@ -5756,10 +5768,10 @@
         <v>15.5</v>
       </c>
       <c r="H140" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I140" s="2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J140" s="2" t="s">
         <v>290</v>
@@ -5767,7 +5779,7 @@
     </row>
     <row r="141" spans="1:10">
       <c r="A141" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B141" s="2">
         <v>46026</v>
@@ -5785,13 +5797,13 @@
         <v>258</v>
       </c>
       <c r="G141" s="2">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="H141" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I141" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J141" s="2" t="s">
         <v>290</v>
@@ -5820,10 +5832,10 @@
         <v>16</v>
       </c>
       <c r="H142" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I142" s="2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J142" s="2" t="s">
         <v>290</v>
@@ -5884,10 +5896,10 @@
         <v>15.5</v>
       </c>
       <c r="H144" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I144" s="2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J144" s="2" t="s">
         <v>290</v>
@@ -5916,10 +5928,10 @@
         <v>15.5</v>
       </c>
       <c r="H145" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I145" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J145" s="2" t="s">
         <v>290</v>
@@ -5945,10 +5957,10 @@
         <v>258</v>
       </c>
       <c r="G146" s="2">
-        <v>15.5</v>
+        <v>19.24</v>
       </c>
       <c r="H146" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I146" s="2">
         <v>0</v>
@@ -5959,7 +5971,7 @@
     </row>
     <row r="147" spans="1:10">
       <c r="A147" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="B147" s="2">
         <v>46026</v>
@@ -5983,7 +5995,7 @@
         <v>0</v>
       </c>
       <c r="I147" s="2">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J147" s="2" t="s">
         <v>290</v>
@@ -6012,10 +6024,10 @@
         <v>16</v>
       </c>
       <c r="H148" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I148" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J148" s="2" t="s">
         <v>290</v>
@@ -6023,7 +6035,7 @@
     </row>
     <row r="149" spans="1:10">
       <c r="A149" s="2" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B149" s="2">
         <v>46026</v>
@@ -6041,10 +6053,10 @@
         <v>258</v>
       </c>
       <c r="G149" s="2">
-        <v>15.5</v>
+        <v>19.15</v>
       </c>
       <c r="H149" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I149" s="2">
         <v>0</v>
@@ -6055,7 +6067,7 @@
     </row>
     <row r="150" spans="1:10">
       <c r="A150" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B150" s="2">
         <v>46026</v>
@@ -6073,13 +6085,13 @@
         <v>258</v>
       </c>
       <c r="G150" s="2">
-        <v>16.67</v>
+        <v>15.5</v>
       </c>
       <c r="H150" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I150" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J150" s="2" t="s">
         <v>290</v>
@@ -6137,13 +6149,13 @@
         <v>258</v>
       </c>
       <c r="G152" s="2">
-        <v>16.48</v>
+        <v>16</v>
       </c>
       <c r="H152" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I152" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J152" s="2" t="s">
         <v>290</v>
@@ -6151,7 +6163,7 @@
     </row>
     <row r="153" spans="1:10">
       <c r="A153" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B153" s="2">
         <v>46026</v>
@@ -6169,10 +6181,10 @@
         <v>258</v>
       </c>
       <c r="G153" s="2">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="H153" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I153" s="2">
         <v>0</v>
@@ -6183,7 +6195,7 @@
     </row>
     <row r="154" spans="1:10">
       <c r="A154" s="2" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B154" s="2">
         <v>46026</v>
@@ -6201,10 +6213,10 @@
         <v>258</v>
       </c>
       <c r="G154" s="2">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="H154" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I154" s="2">
         <v>0</v>
@@ -6215,7 +6227,7 @@
     </row>
     <row r="155" spans="1:10">
       <c r="A155" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B155" s="2">
         <v>46026</v>
@@ -6236,10 +6248,10 @@
         <v>15.5</v>
       </c>
       <c r="H155" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I155" s="2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J155" s="2" t="s">
         <v>290</v>
@@ -6247,7 +6259,7 @@
     </row>
     <row r="156" spans="1:10">
       <c r="A156" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B156" s="2">
         <v>46026</v>
@@ -6268,10 +6280,10 @@
         <v>15.5</v>
       </c>
       <c r="H156" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I156" s="2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J156" s="2" t="s">
         <v>290</v>
@@ -6279,7 +6291,7 @@
     </row>
     <row r="157" spans="1:10">
       <c r="A157" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B157" s="2">
         <v>46026</v>
@@ -6297,10 +6309,10 @@
         <v>258</v>
       </c>
       <c r="G157" s="2">
-        <v>15.5</v>
+        <v>25</v>
       </c>
       <c r="H157" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I157" s="2">
         <v>0</v>
@@ -6311,7 +6323,7 @@
     </row>
     <row r="158" spans="1:10">
       <c r="A158" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B158" s="2">
         <v>46026</v>
@@ -6329,10 +6341,10 @@
         <v>258</v>
       </c>
       <c r="G158" s="2">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="H158" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I158" s="2">
         <v>0</v>
@@ -6343,7 +6355,7 @@
     </row>
     <row r="159" spans="1:10">
       <c r="A159" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B159" s="2">
         <v>46026</v>
@@ -6361,13 +6373,13 @@
         <v>258</v>
       </c>
       <c r="G159" s="2">
+        <v>16</v>
+      </c>
+      <c r="H159" s="2">
+        <v>0</v>
+      </c>
+      <c r="I159" s="2">
         <v>20</v>
-      </c>
-      <c r="H159" s="2">
-        <v>6</v>
-      </c>
-      <c r="I159" s="2">
-        <v>0</v>
       </c>
       <c r="J159" s="2" t="s">
         <v>290</v>
@@ -6375,7 +6387,7 @@
     </row>
     <row r="160" spans="1:10">
       <c r="A160" s="2" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="B160" s="2">
         <v>46026</v>
@@ -6393,13 +6405,13 @@
         <v>258</v>
       </c>
       <c r="G160" s="2">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="H160" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I160" s="2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J160" s="2" t="s">
         <v>290</v>
@@ -6407,7 +6419,7 @@
     </row>
     <row r="161" spans="1:10">
       <c r="A161" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B161" s="2">
         <v>46026</v>
@@ -6428,7 +6440,7 @@
         <v>15.5</v>
       </c>
       <c r="H161" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I161" s="2">
         <v>0</v>
@@ -6439,7 +6451,7 @@
     </row>
     <row r="162" spans="1:10">
       <c r="A162" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B162" s="2">
         <v>46026</v>
@@ -6457,13 +6469,13 @@
         <v>258</v>
       </c>
       <c r="G162" s="2">
-        <v>16</v>
+        <v>23.28</v>
       </c>
       <c r="H162" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I162" s="2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J162" s="2" t="s">
         <v>290</v>
@@ -6471,7 +6483,7 @@
     </row>
     <row r="163" spans="1:10">
       <c r="A163" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B163" s="2">
         <v>46026</v>
@@ -6489,10 +6501,10 @@
         <v>258</v>
       </c>
       <c r="G163" s="2">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="H163" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I163" s="2">
         <v>0</v>
@@ -6503,7 +6515,7 @@
     </row>
     <row r="164" spans="1:10">
       <c r="A164" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B164" s="2">
         <v>46026</v>
@@ -6521,10 +6533,10 @@
         <v>258</v>
       </c>
       <c r="G164" s="2">
-        <v>16</v>
+        <v>16.48</v>
       </c>
       <c r="H164" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I164" s="2">
         <v>0</v>
@@ -6535,7 +6547,7 @@
     </row>
     <row r="165" spans="1:10">
       <c r="A165" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B165" s="2">
         <v>46026</v>
@@ -6553,13 +6565,13 @@
         <v>258</v>
       </c>
       <c r="G165" s="2">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="H165" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I165" s="2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J165" s="2" t="s">
         <v>290</v>
@@ -6570,25 +6582,25 @@
         <v>125</v>
       </c>
       <c r="B166" s="2">
-        <v>46026</v>
+        <v>46026.51171296297</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D166" s="2">
-        <v>46026</v>
+        <v>46026.68966435185</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F166" s="2" t="s">
         <v>258</v>
       </c>
       <c r="G166" s="2">
-        <v>16</v>
+        <v>18.2</v>
       </c>
       <c r="H166" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I166" s="2">
         <v>0</v>
@@ -6617,10 +6629,10 @@
         <v>258</v>
       </c>
       <c r="G167" s="2">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="H167" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I167" s="2">
         <v>0</v>
@@ -6631,7 +6643,7 @@
     </row>
     <row r="168" spans="1:10">
       <c r="A168" s="2" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="B168" s="2">
         <v>46026</v>
@@ -6649,13 +6661,13 @@
         <v>258</v>
       </c>
       <c r="G168" s="2">
-        <v>15.5</v>
+        <v>18.22</v>
       </c>
       <c r="H168" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I168" s="2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J168" s="2" t="s">
         <v>290</v>
@@ -6681,10 +6693,10 @@
         <v>258</v>
       </c>
       <c r="G169" s="2">
-        <v>16</v>
+        <v>18.22</v>
       </c>
       <c r="H169" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I169" s="2">
         <v>0</v>
@@ -6695,7 +6707,7 @@
     </row>
     <row r="170" spans="1:10">
       <c r="A170" s="2" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="B170" s="2">
         <v>46026</v>
@@ -6713,13 +6725,13 @@
         <v>258</v>
       </c>
       <c r="G170" s="2">
-        <v>16.48</v>
+        <v>15.5</v>
       </c>
       <c r="H170" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I170" s="2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J170" s="2" t="s">
         <v>290</v>
@@ -6727,28 +6739,28 @@
     </row>
     <row r="171" spans="1:10">
       <c r="A171" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B171" s="2">
-        <v>46026</v>
+        <v>46026.34715277778</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D171" s="2">
-        <v>46026</v>
+        <v>46026.49857638889</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="F171" s="2" t="s">
         <v>258</v>
       </c>
       <c r="G171" s="2">
-        <v>16.5</v>
+        <v>18.2</v>
       </c>
       <c r="H171" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I171" s="2">
         <v>0</v>
@@ -6759,7 +6771,7 @@
     </row>
     <row r="172" spans="1:10">
       <c r="A172" s="2" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="B172" s="2">
         <v>46026</v>
@@ -6777,13 +6789,13 @@
         <v>258</v>
       </c>
       <c r="G172" s="2">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="H172" s="2">
         <v>0</v>
       </c>
       <c r="I172" s="2">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="J172" s="2" t="s">
         <v>290</v>
@@ -6794,25 +6806,25 @@
         <v>129</v>
       </c>
       <c r="B173" s="2">
-        <v>46026.34715277778</v>
+        <v>46026</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D173" s="2">
-        <v>46026.49857638889</v>
+        <v>46026</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="F173" s="2" t="s">
         <v>258</v>
       </c>
       <c r="G173" s="2">
-        <v>18.2</v>
+        <v>20.03</v>
       </c>
       <c r="H173" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I173" s="2">
         <v>0</v>
@@ -6826,28 +6838,28 @@
         <v>129</v>
       </c>
       <c r="B174" s="2">
-        <v>46026.51171296297</v>
+        <v>46026</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D174" s="2">
-        <v>46026.68966435185</v>
+        <v>46026</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F174" s="2" t="s">
         <v>258</v>
       </c>
       <c r="G174" s="2">
-        <v>18.2</v>
+        <v>20.03</v>
       </c>
       <c r="H174" s="2">
         <v>0</v>
       </c>
       <c r="I174" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J174" s="2" t="s">
         <v>290</v>
@@ -6873,10 +6885,10 @@
         <v>258</v>
       </c>
       <c r="G175" s="2">
-        <v>18.5</v>
+        <v>17.8</v>
       </c>
       <c r="H175" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I175" s="2">
         <v>0</v>
@@ -6905,10 +6917,10 @@
         <v>258</v>
       </c>
       <c r="G176" s="2">
-        <v>19.21</v>
+        <v>30</v>
       </c>
       <c r="H176" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I176" s="2">
         <v>0</v>
@@ -6937,13 +6949,13 @@
         <v>258</v>
       </c>
       <c r="G177" s="2">
-        <v>19.21</v>
+        <v>30</v>
       </c>
       <c r="H177" s="2">
         <v>0</v>
       </c>
       <c r="I177" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J177" s="2" t="s">
         <v>290</v>
@@ -6969,7 +6981,7 @@
         <v>258</v>
       </c>
       <c r="G178" s="2">
-        <v>18.46</v>
+        <v>15.5</v>
       </c>
       <c r="H178" s="2">
         <v>6</v>
@@ -6983,7 +6995,7 @@
     </row>
     <row r="179" spans="1:10">
       <c r="A179" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B179" s="2">
         <v>46026</v>
@@ -7001,13 +7013,13 @@
         <v>258</v>
       </c>
       <c r="G179" s="2">
-        <v>17.43</v>
+        <v>15.5</v>
       </c>
       <c r="H179" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I179" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J179" s="2" t="s">
         <v>290</v>
@@ -7015,7 +7027,7 @@
     </row>
     <row r="180" spans="1:10">
       <c r="A180" s="2" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B180" s="2">
         <v>46026</v>
@@ -7033,7 +7045,7 @@
         <v>258</v>
       </c>
       <c r="G180" s="2">
-        <v>17.8</v>
+        <v>15.5</v>
       </c>
       <c r="H180" s="2">
         <v>7</v>
@@ -7047,7 +7059,7 @@
     </row>
     <row r="181" spans="1:10">
       <c r="A181" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B181" s="2">
         <v>46026</v>
@@ -7065,7 +7077,7 @@
         <v>258</v>
       </c>
       <c r="G181" s="2">
-        <v>30</v>
+        <v>18.5</v>
       </c>
       <c r="H181" s="2">
         <v>8</v>
@@ -7079,7 +7091,7 @@
     </row>
     <row r="182" spans="1:10">
       <c r="A182" s="2" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="B182" s="2">
         <v>46026</v>
@@ -7097,13 +7109,13 @@
         <v>258</v>
       </c>
       <c r="G182" s="2">
-        <v>30</v>
+        <v>16.48</v>
       </c>
       <c r="H182" s="2">
         <v>0</v>
       </c>
       <c r="I182" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J182" s="2" t="s">
         <v>290</v>
@@ -7111,7 +7123,7 @@
     </row>
     <row r="183" spans="1:10">
       <c r="A183" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B183" s="2">
         <v>46026</v>
@@ -7129,10 +7141,10 @@
         <v>258</v>
       </c>
       <c r="G183" s="2">
-        <v>15.5</v>
+        <v>16.67</v>
       </c>
       <c r="H183" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I183" s="2">
         <v>0</v>
@@ -7143,7 +7155,7 @@
     </row>
     <row r="184" spans="1:10">
       <c r="A184" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B184" s="2">
         <v>46026</v>
@@ -7161,10 +7173,10 @@
         <v>258</v>
       </c>
       <c r="G184" s="2">
-        <v>19.21</v>
+        <v>17.43</v>
       </c>
       <c r="H184" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I184" s="2">
         <v>0</v>
@@ -7175,7 +7187,7 @@
     </row>
     <row r="185" spans="1:10">
       <c r="A185" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B185" s="2">
         <v>46026</v>
@@ -7193,7 +7205,7 @@
         <v>258</v>
       </c>
       <c r="G185" s="2">
-        <v>23.28</v>
+        <v>20</v>
       </c>
       <c r="H185" s="2">
         <v>6</v>
@@ -7207,7 +7219,7 @@
     </row>
     <row r="186" spans="1:10">
       <c r="A186" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B186" s="2">
         <v>46026</v>
@@ -7225,10 +7237,10 @@
         <v>258</v>
       </c>
       <c r="G186" s="2">
-        <v>15.5</v>
+        <v>18.46</v>
       </c>
       <c r="H186" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I186" s="2">
         <v>0</v>
@@ -7257,13 +7269,13 @@
         <v>258</v>
       </c>
       <c r="G187" s="2">
-        <v>15.5</v>
+        <v>19.21</v>
       </c>
       <c r="H187" s="2">
         <v>0</v>
       </c>
       <c r="I187" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J187" s="2" t="s">
         <v>290</v>
@@ -7271,7 +7283,7 @@
     </row>
     <row r="188" spans="1:10">
       <c r="A188" s="2" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="B188" s="2">
         <v>46026</v>
@@ -7289,13 +7301,13 @@
         <v>258</v>
       </c>
       <c r="G188" s="2">
-        <v>16</v>
+        <v>18.22</v>
       </c>
       <c r="H188" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I188" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J188" s="2" t="s">
         <v>290</v>
@@ -7303,7 +7315,7 @@
     </row>
     <row r="189" spans="1:10">
       <c r="A189" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B189" s="2">
         <v>46026</v>
@@ -7321,13 +7333,13 @@
         <v>258</v>
       </c>
       <c r="G189" s="2">
-        <v>16</v>
+        <v>19.21</v>
       </c>
       <c r="H189" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I189" s="2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J189" s="2" t="s">
         <v>290</v>
@@ -7335,7 +7347,7 @@
     </row>
     <row r="190" spans="1:10">
       <c r="A190" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B190" s="2">
         <v>46026</v>
@@ -7353,10 +7365,10 @@
         <v>258</v>
       </c>
       <c r="G190" s="2">
-        <v>20.03</v>
+        <v>15.5</v>
       </c>
       <c r="H190" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I190" s="2">
         <v>0</v>
@@ -7367,7 +7379,7 @@
     </row>
     <row r="191" spans="1:10">
       <c r="A191" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B191" s="2">
         <v>46026</v>
@@ -7385,13 +7397,13 @@
         <v>258</v>
       </c>
       <c r="G191" s="2">
-        <v>20.03</v>
+        <v>15.5</v>
       </c>
       <c r="H191" s="2">
         <v>0</v>
       </c>
       <c r="I191" s="2">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J191" s="2" t="s">
         <v>290</v>
@@ -7399,7 +7411,7 @@
     </row>
     <row r="192" spans="1:10">
       <c r="A192" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B192" s="2">
         <v>46026</v>
@@ -7417,10 +7429,10 @@
         <v>258</v>
       </c>
       <c r="G192" s="2">
-        <v>18.22</v>
+        <v>15.5</v>
       </c>
       <c r="H192" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I192" s="2">
         <v>0</v>
@@ -7431,7 +7443,7 @@
     </row>
     <row r="193" spans="1:10">
       <c r="A193" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B193" s="2">
         <v>46026</v>
@@ -7449,7 +7461,7 @@
         <v>258</v>
       </c>
       <c r="G193" s="2">
-        <v>18.22</v>
+        <v>19.21</v>
       </c>
       <c r="H193" s="2">
         <v>1</v>
@@ -7481,13 +7493,13 @@
         <v>258</v>
       </c>
       <c r="G194" s="2">
-        <v>18.22</v>
+        <v>18.5</v>
       </c>
       <c r="H194" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I194" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J194" s="2" t="s">
         <v>290</v>
@@ -7495,7 +7507,7 @@
     </row>
     <row r="195" spans="1:10">
       <c r="A195" s="2" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B195" s="2">
         <v>46026</v>
@@ -7516,10 +7528,10 @@
         <v>15.5</v>
       </c>
       <c r="H195" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I195" s="2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J195" s="2" t="s">
         <v>290</v>
@@ -7530,13 +7542,13 @@
         <v>142</v>
       </c>
       <c r="B196" s="2">
-        <v>46026.33484953704</v>
+        <v>46026.36542824074</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D196" s="2">
-        <v>46026.66297453704</v>
+        <v>46026.6649537037</v>
       </c>
       <c r="E196" s="2" t="s">
         <v>247</v>
@@ -7562,13 +7574,13 @@
         <v>143</v>
       </c>
       <c r="B197" s="2">
-        <v>46026.36542824074</v>
+        <v>46026.33484953704</v>
       </c>
       <c r="C197" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D197" s="2">
-        <v>46026.6649537037</v>
+        <v>46026.66297453704</v>
       </c>
       <c r="E197" s="2" t="s">
         <v>247</v>
@@ -7591,7 +7603,7 @@
     </row>
     <row r="198" spans="1:10">
       <c r="A198" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B198" s="2">
         <v>46026.54024305556</v>
@@ -7658,13 +7670,13 @@
         <v>145</v>
       </c>
       <c r="B200" s="2">
-        <v>46026.60745370371</v>
+        <v>46026.33850694444</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D200" s="2">
-        <v>46026.71085648148</v>
+        <v>46026.70988425926</v>
       </c>
       <c r="E200" s="2" t="s">
         <v>247</v>
@@ -7673,7 +7685,7 @@
         <v>261</v>
       </c>
       <c r="G200" s="2">
-        <v>15.16</v>
+        <v>18</v>
       </c>
       <c r="H200" s="2">
         <v>0</v>
@@ -7687,19 +7699,19 @@
     </row>
     <row r="201" spans="1:10">
       <c r="A201" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B201" s="2">
-        <v>46026.32675925926</v>
+        <v>46026.60745370371</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D201" s="2">
-        <v>46026.57659722222</v>
+        <v>46026.71085648148</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F201" s="2" t="s">
         <v>261</v>
@@ -7719,7 +7731,7 @@
     </row>
     <row r="202" spans="1:10">
       <c r="A202" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B202" s="2">
         <v>46026.33873842593</v>
@@ -7747,25 +7759,25 @@
     </row>
     <row r="203" spans="1:10">
       <c r="A203" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B203" s="2">
-        <v>46026.33850694444</v>
+        <v>46026.32675925926</v>
       </c>
       <c r="C203" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D203" s="2">
-        <v>46026.70988425926</v>
+        <v>46026.57659722222</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F203" s="2" t="s">
         <v>261</v>
       </c>
       <c r="G203" s="2">
-        <v>18</v>
+        <v>15.16</v>
       </c>
       <c r="H203" s="2">
         <v>0</v>
@@ -7782,25 +7794,25 @@
         <v>148</v>
       </c>
       <c r="B204" s="2">
-        <v>46026.33802083333</v>
+        <v>46026.33333333334</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D204" s="2">
-        <v>46026.66784722222</v>
+        <v>46026.33333333334</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F204" s="2" t="s">
         <v>262</v>
       </c>
       <c r="G204" s="2">
-        <v>18</v>
+        <v>15.16</v>
       </c>
       <c r="H204" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I204" s="2">
         <v>0</v>
@@ -7878,25 +7890,25 @@
         <v>150</v>
       </c>
       <c r="B207" s="2">
-        <v>46026.33333333334</v>
+        <v>46026.32189814815</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D207" s="2">
-        <v>46026.33333333334</v>
+        <v>46026.67254629629</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F207" s="2" t="s">
         <v>262</v>
       </c>
       <c r="G207" s="2">
-        <v>15.16</v>
+        <v>24</v>
       </c>
       <c r="H207" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I207" s="2">
         <v>0</v>
@@ -7910,13 +7922,13 @@
         <v>151</v>
       </c>
       <c r="B208" s="2">
-        <v>46026.33658564815</v>
+        <v>46026.34234953704</v>
       </c>
       <c r="C208" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D208" s="2">
-        <v>46026.65758101852</v>
+        <v>46026.68875</v>
       </c>
       <c r="E208" s="2" t="s">
         <v>247</v>
@@ -7925,7 +7937,7 @@
         <v>262</v>
       </c>
       <c r="G208" s="2">
-        <v>15.16</v>
+        <v>21</v>
       </c>
       <c r="H208" s="2">
         <v>0</v>
@@ -7942,13 +7954,13 @@
         <v>152</v>
       </c>
       <c r="B209" s="2">
-        <v>46026.32084490741</v>
+        <v>46026.3243287037</v>
       </c>
       <c r="C209" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D209" s="2">
-        <v>46026.65834490741</v>
+        <v>46026.66666666666</v>
       </c>
       <c r="E209" s="2" t="s">
         <v>247</v>
@@ -7957,7 +7969,7 @@
         <v>262</v>
       </c>
       <c r="G209" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H209" s="2">
         <v>0</v>
@@ -7974,13 +7986,13 @@
         <v>153</v>
       </c>
       <c r="B210" s="2">
-        <v>46026.33702546296</v>
+        <v>46026.33658564815</v>
       </c>
       <c r="C210" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D210" s="2">
-        <v>46026.65006944445</v>
+        <v>46026.65758101852</v>
       </c>
       <c r="E210" s="2" t="s">
         <v>247</v>
@@ -7989,7 +8001,7 @@
         <v>262</v>
       </c>
       <c r="G210" s="2">
-        <v>12.14</v>
+        <v>15.16</v>
       </c>
       <c r="H210" s="2">
         <v>0</v>
@@ -8006,18 +8018,22 @@
         <v>154</v>
       </c>
       <c r="B211" s="2">
-        <v>46026.3243287037</v>
+        <v>46026.32084490741</v>
       </c>
       <c r="C211" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="D211" s="2"/>
-      <c r="E211" s="2"/>
+      <c r="D211" s="2">
+        <v>46026.65834490741</v>
+      </c>
+      <c r="E211" s="2" t="s">
+        <v>247</v>
+      </c>
       <c r="F211" s="2" t="s">
         <v>262</v>
       </c>
       <c r="G211" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H211" s="2">
         <v>0</v>
@@ -8034,13 +8050,13 @@
         <v>155</v>
       </c>
       <c r="B212" s="2">
-        <v>46026.34693287037</v>
+        <v>46026.33802083333</v>
       </c>
       <c r="C212" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D212" s="2">
-        <v>46026.65140046296</v>
+        <v>46026.66784722222</v>
       </c>
       <c r="E212" s="2" t="s">
         <v>247</v>
@@ -8049,7 +8065,7 @@
         <v>262</v>
       </c>
       <c r="G212" s="2">
-        <v>15.16</v>
+        <v>18</v>
       </c>
       <c r="H212" s="2">
         <v>0</v>
@@ -8066,13 +8082,13 @@
         <v>156</v>
       </c>
       <c r="B213" s="2">
-        <v>46026.34234953704</v>
+        <v>46026.33702546296</v>
       </c>
       <c r="C213" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D213" s="2">
-        <v>46026.68875</v>
+        <v>46026.65006944445</v>
       </c>
       <c r="E213" s="2" t="s">
         <v>247</v>
@@ -8081,7 +8097,7 @@
         <v>262</v>
       </c>
       <c r="G213" s="2">
-        <v>21</v>
+        <v>12.14</v>
       </c>
       <c r="H213" s="2">
         <v>0</v>
@@ -8098,13 +8114,13 @@
         <v>157</v>
       </c>
       <c r="B214" s="2">
-        <v>46026.32189814815</v>
+        <v>46026.34693287037</v>
       </c>
       <c r="C214" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D214" s="2">
-        <v>46026.67254629629</v>
+        <v>46026.65140046296</v>
       </c>
       <c r="E214" s="2" t="s">
         <v>247</v>
@@ -8113,7 +8129,7 @@
         <v>262</v>
       </c>
       <c r="G214" s="2">
-        <v>24</v>
+        <v>15.16</v>
       </c>
       <c r="H214" s="2">
         <v>0</v>
@@ -8254,13 +8270,13 @@
         <v>162</v>
       </c>
       <c r="B219" s="2">
-        <v>46026.29328703704</v>
+        <v>46026.57570601852</v>
       </c>
       <c r="C219" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D219" s="2">
-        <v>46026.5584375</v>
+        <v>46026.9321875</v>
       </c>
       <c r="E219" s="2" t="s">
         <v>247</v>
@@ -8269,7 +8285,7 @@
         <v>264</v>
       </c>
       <c r="G219" s="2">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H219" s="2">
         <v>0</v>
@@ -8286,13 +8302,13 @@
         <v>163</v>
       </c>
       <c r="B220" s="2">
-        <v>46026.57570601852</v>
+        <v>46026.29328703704</v>
       </c>
       <c r="C220" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D220" s="2">
-        <v>46026.9321875</v>
+        <v>46026.5584375</v>
       </c>
       <c r="E220" s="2" t="s">
         <v>247</v>
@@ -8301,7 +8317,7 @@
         <v>264</v>
       </c>
       <c r="G220" s="2">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H220" s="2">
         <v>0</v>
@@ -8318,13 +8334,13 @@
         <v>164</v>
       </c>
       <c r="B221" s="2">
-        <v>46026.33045138889</v>
+        <v>46026.61806712963</v>
       </c>
       <c r="C221" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D221" s="2">
-        <v>46026.66667824074</v>
+        <v>46026.89246527778</v>
       </c>
       <c r="E221" s="2" t="s">
         <v>247</v>
@@ -8333,7 +8349,7 @@
         <v>265</v>
       </c>
       <c r="G221" s="2">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H221" s="2">
         <v>0</v>
@@ -8350,13 +8366,13 @@
         <v>165</v>
       </c>
       <c r="B222" s="2">
-        <v>46026.39515046297</v>
+        <v>46026.62165509259</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D222" s="2">
-        <v>46026.62520833333</v>
+        <v>46026.66582175926</v>
       </c>
       <c r="E222" s="2" t="s">
         <v>247</v>
@@ -8365,7 +8381,7 @@
         <v>265</v>
       </c>
       <c r="G222" s="2">
-        <v>15.16</v>
+        <v>18.5</v>
       </c>
       <c r="H222" s="2">
         <v>0</v>
@@ -8379,25 +8395,25 @@
     </row>
     <row r="223" spans="1:10">
       <c r="A223" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B223" s="2">
-        <v>46026.37482638889</v>
+        <v>46026.33035879629</v>
       </c>
       <c r="C223" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D223" s="2">
-        <v>46026.66260416667</v>
+        <v>46026.59949074074</v>
       </c>
       <c r="E223" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F223" s="2" t="s">
         <v>265</v>
       </c>
       <c r="G223" s="2">
-        <v>15.16</v>
+        <v>18.5</v>
       </c>
       <c r="H223" s="2">
         <v>0</v>
@@ -8411,28 +8427,28 @@
     </row>
     <row r="224" spans="1:10">
       <c r="A224" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B224" s="2">
-        <v>46026.33333333334</v>
+        <v>46026.58440972222</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D224" s="2">
-        <v>46026.33333333334</v>
+        <v>46026.87471064815</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F224" s="2" t="s">
         <v>265</v>
       </c>
       <c r="G224" s="2">
-        <v>15.16</v>
+        <v>18</v>
       </c>
       <c r="H224" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I224" s="2">
         <v>0</v>
@@ -8443,19 +8459,19 @@
     </row>
     <row r="225" spans="1:10">
       <c r="A225" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B225" s="2">
-        <v>46026.33333333334</v>
+        <v>46026.39515046297</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D225" s="2">
-        <v>46026.33333333334</v>
+        <v>46026.62520833333</v>
       </c>
       <c r="E225" s="2" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F225" s="2" t="s">
         <v>265</v>
@@ -8464,7 +8480,7 @@
         <v>15.16</v>
       </c>
       <c r="H225" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I225" s="2">
         <v>0</v>
@@ -8475,28 +8491,28 @@
     </row>
     <row r="226" spans="1:10">
       <c r="A226" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B226" s="2">
-        <v>46026.58991898148</v>
+        <v>46026.33333333334</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D226" s="2">
-        <v>46026.88664351852</v>
+        <v>46026.33333333334</v>
       </c>
       <c r="E226" s="2" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F226" s="2" t="s">
         <v>265</v>
       </c>
       <c r="G226" s="2">
-        <v>23</v>
+        <v>15.16</v>
       </c>
       <c r="H226" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I226" s="2">
         <v>0</v>
@@ -8507,16 +8523,16 @@
     </row>
     <row r="227" spans="1:10">
       <c r="A227" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B227" s="2">
-        <v>46026.66313657408</v>
+        <v>46026.37482638889</v>
       </c>
       <c r="C227" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D227" s="2">
-        <v>46026.84418981482</v>
+        <v>46026.66260416667</v>
       </c>
       <c r="E227" s="2" t="s">
         <v>247</v>
@@ -8525,7 +8541,7 @@
         <v>265</v>
       </c>
       <c r="G227" s="2">
-        <v>24</v>
+        <v>15.16</v>
       </c>
       <c r="H227" s="2">
         <v>0</v>
@@ -8539,25 +8555,25 @@
     </row>
     <row r="228" spans="1:10">
       <c r="A228" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B228" s="2">
-        <v>46026.33035879629</v>
+        <v>46026.41596064815</v>
       </c>
       <c r="C228" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D228" s="2">
-        <v>46026.59949074074</v>
+        <v>46026.71364583333</v>
       </c>
       <c r="E228" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F228" s="2" t="s">
         <v>265</v>
       </c>
       <c r="G228" s="2">
-        <v>18.5</v>
+        <v>15.16</v>
       </c>
       <c r="H228" s="2">
         <v>0</v>
@@ -8571,16 +8587,16 @@
     </row>
     <row r="229" spans="1:10">
       <c r="A229" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B229" s="2">
-        <v>46026.58440972222</v>
+        <v>46026.47503472222</v>
       </c>
       <c r="C229" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D229" s="2">
-        <v>46026.87471064815</v>
+        <v>46026.81950231481</v>
       </c>
       <c r="E229" s="2" t="s">
         <v>247</v>
@@ -8589,7 +8605,7 @@
         <v>265</v>
       </c>
       <c r="G229" s="2">
-        <v>18</v>
+        <v>15.16</v>
       </c>
       <c r="H229" s="2">
         <v>0</v>
@@ -8603,16 +8619,16 @@
     </row>
     <row r="230" spans="1:10">
       <c r="A230" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B230" s="2">
-        <v>46026.41596064815</v>
+        <v>46026.58991898148</v>
       </c>
       <c r="C230" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D230" s="2">
-        <v>46026.71364583333</v>
+        <v>46026.88664351852</v>
       </c>
       <c r="E230" s="2" t="s">
         <v>247</v>
@@ -8621,7 +8637,7 @@
         <v>265</v>
       </c>
       <c r="G230" s="2">
-        <v>15.16</v>
+        <v>23</v>
       </c>
       <c r="H230" s="2">
         <v>0</v>
@@ -8635,19 +8651,19 @@
     </row>
     <row r="231" spans="1:10">
       <c r="A231" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B231" s="2">
-        <v>46026.47503472222</v>
+        <v>46026.33333333334</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D231" s="2">
-        <v>46026.81950231481</v>
+        <v>46026.33333333334</v>
       </c>
       <c r="E231" s="2" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F231" s="2" t="s">
         <v>265</v>
@@ -8656,7 +8672,7 @@
         <v>15.16</v>
       </c>
       <c r="H231" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I231" s="2">
         <v>0</v>
@@ -8667,21 +8683,25 @@
     </row>
     <row r="232" spans="1:10">
       <c r="A232" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B232" s="2">
-        <v>46026.33443287037</v>
+        <v>46026.33045138889</v>
       </c>
       <c r="C232" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="D232" s="2"/>
-      <c r="E232" s="2"/>
+      <c r="D232" s="2">
+        <v>46026.66667824074</v>
+      </c>
+      <c r="E232" s="2" t="s">
+        <v>247</v>
+      </c>
       <c r="F232" s="2" t="s">
         <v>265</v>
       </c>
       <c r="G232" s="2">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H232" s="2">
         <v>0</v>
@@ -8695,20 +8715,16 @@
     </row>
     <row r="233" spans="1:10">
       <c r="A233" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B233" s="2">
-        <v>46026.61806712963</v>
+        <v>46026.33443287037</v>
       </c>
       <c r="C233" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="D233" s="2">
-        <v>46026.89246527778</v>
-      </c>
-      <c r="E233" s="2" t="s">
-        <v>247</v>
-      </c>
+      <c r="D233" s="2"/>
+      <c r="E233" s="2"/>
       <c r="F233" s="2" t="s">
         <v>265</v>
       </c>
@@ -8727,16 +8743,16 @@
     </row>
     <row r="234" spans="1:10">
       <c r="A234" s="2" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B234" s="2">
-        <v>46026.62165509259</v>
+        <v>46026.66313657408</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D234" s="2">
-        <v>46026.66582175926</v>
+        <v>46026.84418981482</v>
       </c>
       <c r="E234" s="2" t="s">
         <v>247</v>
@@ -8745,7 +8761,7 @@
         <v>265</v>
       </c>
       <c r="G234" s="2">
-        <v>18.5</v>
+        <v>24</v>
       </c>
       <c r="H234" s="2">
         <v>0</v>
@@ -8794,13 +8810,13 @@
         <v>178</v>
       </c>
       <c r="B236" s="2">
-        <v>46026.37188657407</v>
+        <v>46026.32957175926</v>
       </c>
       <c r="C236" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D236" s="2">
-        <v>46026.7583912037</v>
+        <v>46026.66822916667</v>
       </c>
       <c r="E236" s="2" t="s">
         <v>247</v>
@@ -8809,7 +8825,7 @@
         <v>266</v>
       </c>
       <c r="G236" s="2">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H236" s="2">
         <v>0</v>
@@ -8826,13 +8842,13 @@
         <v>179</v>
       </c>
       <c r="B237" s="2">
-        <v>46026.57556712963</v>
+        <v>46026.38270833333</v>
       </c>
       <c r="C237" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D237" s="2">
-        <v>46026.93673611111</v>
+        <v>46026.71809027778</v>
       </c>
       <c r="E237" s="2" t="s">
         <v>247</v>
@@ -8841,7 +8857,7 @@
         <v>266</v>
       </c>
       <c r="G237" s="2">
-        <v>22</v>
+        <v>15.16</v>
       </c>
       <c r="H237" s="2">
         <v>0</v>
@@ -8858,13 +8874,13 @@
         <v>180</v>
       </c>
       <c r="B238" s="2">
-        <v>46026.32957175926</v>
+        <v>46026.33930555556</v>
       </c>
       <c r="C238" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D238" s="2">
-        <v>46026.66822916667</v>
+        <v>46026.7229050926</v>
       </c>
       <c r="E238" s="2" t="s">
         <v>247</v>
@@ -8873,7 +8889,7 @@
         <v>266</v>
       </c>
       <c r="G238" s="2">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H238" s="2">
         <v>0</v>
@@ -8890,13 +8906,13 @@
         <v>181</v>
       </c>
       <c r="B239" s="2">
-        <v>46026.70944444444</v>
+        <v>46026.33363425926</v>
       </c>
       <c r="C239" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D239" s="2">
-        <v>46026.70946759259</v>
+        <v>46026.68724537037</v>
       </c>
       <c r="E239" s="2" t="s">
         <v>247</v>
@@ -8905,7 +8921,7 @@
         <v>266</v>
       </c>
       <c r="G239" s="2">
-        <v>20</v>
+        <v>15.16</v>
       </c>
       <c r="H239" s="2">
         <v>0</v>
@@ -8922,13 +8938,13 @@
         <v>182</v>
       </c>
       <c r="B240" s="2">
-        <v>46026.38131944444</v>
+        <v>46026.63365740741</v>
       </c>
       <c r="C240" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D240" s="2">
-        <v>46026.67119212963</v>
+        <v>46026.9155787037</v>
       </c>
       <c r="E240" s="2" t="s">
         <v>247</v>
@@ -8937,7 +8953,7 @@
         <v>266</v>
       </c>
       <c r="G240" s="2">
-        <v>12.14</v>
+        <v>18</v>
       </c>
       <c r="H240" s="2">
         <v>0</v>
@@ -8954,13 +8970,13 @@
         <v>183</v>
       </c>
       <c r="B241" s="2">
-        <v>46026.36924768519</v>
+        <v>46026.58028935185</v>
       </c>
       <c r="C241" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D241" s="2">
-        <v>46026.73643518519</v>
+        <v>46026.93655092592</v>
       </c>
       <c r="E241" s="2" t="s">
         <v>247</v>
@@ -8969,7 +8985,7 @@
         <v>266</v>
       </c>
       <c r="G241" s="2">
-        <v>12.14</v>
+        <v>24</v>
       </c>
       <c r="H241" s="2">
         <v>0</v>
@@ -8986,13 +9002,13 @@
         <v>184</v>
       </c>
       <c r="B242" s="2">
-        <v>46026.33930555556</v>
+        <v>46026.36924768519</v>
       </c>
       <c r="C242" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D242" s="2">
-        <v>46026.7229050926</v>
+        <v>46026.73643518519</v>
       </c>
       <c r="E242" s="2" t="s">
         <v>247</v>
@@ -9001,7 +9017,7 @@
         <v>266</v>
       </c>
       <c r="G242" s="2">
-        <v>25</v>
+        <v>12.14</v>
       </c>
       <c r="H242" s="2">
         <v>0</v>
@@ -9018,13 +9034,13 @@
         <v>185</v>
       </c>
       <c r="B243" s="2">
-        <v>46026.33363425926</v>
+        <v>46026.37188657407</v>
       </c>
       <c r="C243" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D243" s="2">
-        <v>46026.68724537037</v>
+        <v>46026.7583912037</v>
       </c>
       <c r="E243" s="2" t="s">
         <v>247</v>
@@ -9033,7 +9049,7 @@
         <v>266</v>
       </c>
       <c r="G243" s="2">
-        <v>15.16</v>
+        <v>13</v>
       </c>
       <c r="H243" s="2">
         <v>0</v>
@@ -9050,13 +9066,13 @@
         <v>186</v>
       </c>
       <c r="B244" s="2">
-        <v>46026.63365740741</v>
+        <v>46026.38131944444</v>
       </c>
       <c r="C244" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D244" s="2">
-        <v>46026.9155787037</v>
+        <v>46026.67119212963</v>
       </c>
       <c r="E244" s="2" t="s">
         <v>247</v>
@@ -9065,7 +9081,7 @@
         <v>266</v>
       </c>
       <c r="G244" s="2">
-        <v>18</v>
+        <v>12.14</v>
       </c>
       <c r="H244" s="2">
         <v>0</v>
@@ -9082,13 +9098,13 @@
         <v>187</v>
       </c>
       <c r="B245" s="2">
-        <v>46026.58028935185</v>
+        <v>46026.70944444444</v>
       </c>
       <c r="C245" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D245" s="2">
-        <v>46026.93655092592</v>
+        <v>46026.70946759259</v>
       </c>
       <c r="E245" s="2" t="s">
         <v>247</v>
@@ -9097,7 +9113,7 @@
         <v>266</v>
       </c>
       <c r="G245" s="2">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H245" s="2">
         <v>0</v>
@@ -9114,22 +9130,22 @@
         <v>188</v>
       </c>
       <c r="B246" s="2">
-        <v>46026.33704861111</v>
+        <v>46026.73431712963</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D246" s="2">
-        <v>46026.50766203704</v>
+        <v>46026.7343287037</v>
       </c>
       <c r="E246" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F246" s="2" t="s">
         <v>266</v>
       </c>
       <c r="G246" s="2">
-        <v>21</v>
+        <v>12.14</v>
       </c>
       <c r="H246" s="2">
         <v>0</v>
@@ -9146,22 +9162,22 @@
         <v>188</v>
       </c>
       <c r="B247" s="2">
-        <v>46026.52739583333</v>
+        <v>46026.42145833333</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D247" s="2">
-        <v>46026.63332175926</v>
+        <v>46026.73428240741</v>
       </c>
       <c r="E247" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F247" s="2" t="s">
         <v>266</v>
       </c>
       <c r="G247" s="2">
-        <v>21</v>
+        <v>12.14</v>
       </c>
       <c r="H247" s="2">
         <v>0</v>
@@ -9178,25 +9194,25 @@
         <v>189</v>
       </c>
       <c r="B248" s="2">
-        <v>46026.32795138889</v>
+        <v>46026.33333333334</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D248" s="2">
-        <v>46026.42746527777</v>
+        <v>46026.33333333334</v>
       </c>
       <c r="E248" s="2" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F248" s="2" t="s">
         <v>266</v>
       </c>
       <c r="G248" s="2">
-        <v>22</v>
+        <v>12.14</v>
       </c>
       <c r="H248" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I248" s="2">
         <v>0</v>
@@ -9210,13 +9226,13 @@
         <v>190</v>
       </c>
       <c r="B249" s="2">
-        <v>46026.62496527778</v>
+        <v>46026.62092592593</v>
       </c>
       <c r="C249" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D249" s="2">
-        <v>46026.90383101852</v>
+        <v>46026.87697916666</v>
       </c>
       <c r="E249" s="2" t="s">
         <v>247</v>
@@ -9225,7 +9241,7 @@
         <v>266</v>
       </c>
       <c r="G249" s="2">
-        <v>20</v>
+        <v>12.14</v>
       </c>
       <c r="H249" s="2">
         <v>0</v>
@@ -9242,13 +9258,13 @@
         <v>191</v>
       </c>
       <c r="B250" s="2">
-        <v>46026.62092592593</v>
+        <v>46026.62496527778</v>
       </c>
       <c r="C250" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D250" s="2">
-        <v>46026.87697916666</v>
+        <v>46026.90383101852</v>
       </c>
       <c r="E250" s="2" t="s">
         <v>247</v>
@@ -9257,7 +9273,7 @@
         <v>266</v>
       </c>
       <c r="G250" s="2">
-        <v>12.14</v>
+        <v>20</v>
       </c>
       <c r="H250" s="2">
         <v>0</v>
@@ -9274,25 +9290,25 @@
         <v>192</v>
       </c>
       <c r="B251" s="2">
-        <v>46026.33333333334</v>
+        <v>46026.32795138889</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D251" s="2">
-        <v>46026.33333333334</v>
+        <v>46026.42746527777</v>
       </c>
       <c r="E251" s="2" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F251" s="2" t="s">
         <v>266</v>
       </c>
       <c r="G251" s="2">
-        <v>12.14</v>
+        <v>22</v>
       </c>
       <c r="H251" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I251" s="2">
         <v>0</v>
@@ -9306,13 +9322,13 @@
         <v>193</v>
       </c>
       <c r="B252" s="2">
-        <v>46026.42145833333</v>
+        <v>46026.33704861111</v>
       </c>
       <c r="C252" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D252" s="2">
-        <v>46026.73428240741</v>
+        <v>46026.50766203704</v>
       </c>
       <c r="E252" s="2" t="s">
         <v>248</v>
@@ -9321,7 +9337,7 @@
         <v>266</v>
       </c>
       <c r="G252" s="2">
-        <v>12.14</v>
+        <v>21</v>
       </c>
       <c r="H252" s="2">
         <v>0</v>
@@ -9335,16 +9351,16 @@
     </row>
     <row r="253" spans="1:10">
       <c r="A253" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B253" s="2">
-        <v>46026.73431712963</v>
+        <v>46026.57556712963</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D253" s="2">
-        <v>46026.7343287037</v>
+        <v>46026.93673611111</v>
       </c>
       <c r="E253" s="2" t="s">
         <v>247</v>
@@ -9353,7 +9369,7 @@
         <v>266</v>
       </c>
       <c r="G253" s="2">
-        <v>12.14</v>
+        <v>22</v>
       </c>
       <c r="H253" s="2">
         <v>0</v>
@@ -9367,16 +9383,16 @@
     </row>
     <row r="254" spans="1:10">
       <c r="A254" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B254" s="2">
-        <v>46026.58234953704</v>
+        <v>46026.52739583333</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D254" s="2">
-        <v>46026.9369212963</v>
+        <v>46026.63332175926</v>
       </c>
       <c r="E254" s="2" t="s">
         <v>247</v>
@@ -9385,7 +9401,7 @@
         <v>266</v>
       </c>
       <c r="G254" s="2">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H254" s="2">
         <v>0</v>
@@ -9402,13 +9418,13 @@
         <v>195</v>
       </c>
       <c r="B255" s="2">
-        <v>46026.38270833333</v>
+        <v>46026.58234953704</v>
       </c>
       <c r="C255" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D255" s="2">
-        <v>46026.71809027778</v>
+        <v>46026.9369212963</v>
       </c>
       <c r="E255" s="2" t="s">
         <v>247</v>
@@ -9417,7 +9433,7 @@
         <v>266</v>
       </c>
       <c r="G255" s="2">
-        <v>15.16</v>
+        <v>17</v>
       </c>
       <c r="H255" s="2">
         <v>0</v>
@@ -9498,22 +9514,18 @@
         <v>198</v>
       </c>
       <c r="B258" s="2">
-        <v>46026.64784722222</v>
+        <v>46026.94660879629</v>
       </c>
       <c r="C258" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="D258" s="2">
-        <v>46026.87841435185</v>
-      </c>
-      <c r="E258" s="2" t="s">
-        <v>247</v>
-      </c>
+      <c r="D258" s="2"/>
+      <c r="E258" s="2"/>
       <c r="F258" s="2" t="s">
         <v>268</v>
       </c>
       <c r="G258" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H258" s="2">
         <v>0</v>
@@ -9530,18 +9542,22 @@
         <v>199</v>
       </c>
       <c r="B259" s="2">
-        <v>46026.94660879629</v>
+        <v>46026.42</v>
       </c>
       <c r="C259" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="D259" s="2"/>
-      <c r="E259" s="2"/>
+      <c r="D259" s="2">
+        <v>46026.76138888889</v>
+      </c>
+      <c r="E259" s="2" t="s">
+        <v>247</v>
+      </c>
       <c r="F259" s="2" t="s">
         <v>268</v>
       </c>
       <c r="G259" s="2">
-        <v>17</v>
+        <v>26.1</v>
       </c>
       <c r="H259" s="2">
         <v>0</v>
@@ -9558,13 +9574,13 @@
         <v>200</v>
       </c>
       <c r="B260" s="2">
-        <v>46026.42</v>
+        <v>46026.49403935186</v>
       </c>
       <c r="C260" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D260" s="2">
-        <v>46026.76138888889</v>
+        <v>46026.84424768519</v>
       </c>
       <c r="E260" s="2" t="s">
         <v>247</v>
@@ -9573,7 +9589,7 @@
         <v>268</v>
       </c>
       <c r="G260" s="2">
-        <v>26.1</v>
+        <v>19</v>
       </c>
       <c r="H260" s="2">
         <v>0</v>
@@ -9590,13 +9606,13 @@
         <v>201</v>
       </c>
       <c r="B261" s="2">
-        <v>46026.49403935186</v>
+        <v>46026.45079861111</v>
       </c>
       <c r="C261" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D261" s="2">
-        <v>46026.84424768519</v>
+        <v>46026.96371527778</v>
       </c>
       <c r="E261" s="2" t="s">
         <v>247</v>
@@ -9605,7 +9621,7 @@
         <v>268</v>
       </c>
       <c r="G261" s="2">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="H261" s="2">
         <v>0</v>
@@ -9622,13 +9638,13 @@
         <v>202</v>
       </c>
       <c r="B262" s="2">
-        <v>46026.45079861111</v>
+        <v>46026.64784722222</v>
       </c>
       <c r="C262" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D262" s="2">
-        <v>46026.96371527778</v>
+        <v>46026.87841435185</v>
       </c>
       <c r="E262" s="2" t="s">
         <v>247</v>
@@ -9637,7 +9653,7 @@
         <v>268</v>
       </c>
       <c r="G262" s="2">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="H262" s="2">
         <v>0</v>
@@ -9654,13 +9670,13 @@
         <v>203</v>
       </c>
       <c r="B263" s="2">
-        <v>46026.39563657407</v>
+        <v>46026.41972222222</v>
       </c>
       <c r="C263" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D263" s="2">
-        <v>46026.39881944445</v>
+        <v>46026.72821759259</v>
       </c>
       <c r="E263" s="2" t="s">
         <v>247</v>
@@ -9669,7 +9685,7 @@
         <v>269</v>
       </c>
       <c r="G263" s="2">
-        <v>17.54</v>
+        <v>15.16</v>
       </c>
       <c r="H263" s="2">
         <v>0</v>
@@ -9686,13 +9702,13 @@
         <v>204</v>
       </c>
       <c r="B264" s="2">
-        <v>46026.63527777778</v>
+        <v>46026.39548611111</v>
       </c>
       <c r="C264" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D264" s="2">
-        <v>46026.92057870371</v>
+        <v>46026.69171296297</v>
       </c>
       <c r="E264" s="2" t="s">
         <v>247</v>
@@ -9701,7 +9717,7 @@
         <v>269</v>
       </c>
       <c r="G264" s="2">
-        <v>16</v>
+        <v>17.37</v>
       </c>
       <c r="H264" s="2">
         <v>0</v>
@@ -9718,13 +9734,13 @@
         <v>205</v>
       </c>
       <c r="B265" s="2">
-        <v>46026.39548611111</v>
+        <v>46026.63527777778</v>
       </c>
       <c r="C265" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D265" s="2">
-        <v>46026.69171296297</v>
+        <v>46026.92057870371</v>
       </c>
       <c r="E265" s="2" t="s">
         <v>247</v>
@@ -9733,7 +9749,7 @@
         <v>269</v>
       </c>
       <c r="G265" s="2">
-        <v>17.37</v>
+        <v>16</v>
       </c>
       <c r="H265" s="2">
         <v>0</v>
@@ -9782,13 +9798,13 @@
         <v>207</v>
       </c>
       <c r="B267" s="2">
-        <v>46026.41972222222</v>
+        <v>46026.39563657407</v>
       </c>
       <c r="C267" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D267" s="2">
-        <v>46026.72821759259</v>
+        <v>46026.39881944445</v>
       </c>
       <c r="E267" s="2" t="s">
         <v>247</v>
@@ -9797,7 +9813,7 @@
         <v>269</v>
       </c>
       <c r="G267" s="2">
-        <v>15.16</v>
+        <v>17.54</v>
       </c>
       <c r="H267" s="2">
         <v>0</v>
@@ -9842,13 +9858,13 @@
         <v>209</v>
       </c>
       <c r="B269" s="2">
-        <v>46026.32759259259</v>
+        <v>46026.33460648148</v>
       </c>
       <c r="C269" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D269" s="2">
-        <v>46026.74381944445</v>
+        <v>46026.67572916667</v>
       </c>
       <c r="E269" s="2" t="s">
         <v>247</v>
@@ -9857,7 +9873,7 @@
         <v>271</v>
       </c>
       <c r="G269" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H269" s="2">
         <v>0</v>
@@ -9874,13 +9890,13 @@
         <v>210</v>
       </c>
       <c r="B270" s="2">
-        <v>46026.33460648148</v>
+        <v>46026.32759259259</v>
       </c>
       <c r="C270" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D270" s="2">
-        <v>46026.67572916667</v>
+        <v>46026.74381944445</v>
       </c>
       <c r="E270" s="2" t="s">
         <v>247</v>
@@ -9889,7 +9905,7 @@
         <v>271</v>
       </c>
       <c r="G270" s="2">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H270" s="2">
         <v>0</v>
@@ -9938,13 +9954,13 @@
         <v>212</v>
       </c>
       <c r="B272" s="2">
-        <v>46026.58375</v>
+        <v>46026.71427083333</v>
       </c>
       <c r="C272" s="2" t="s">
         <v>243</v>
       </c>
       <c r="D272" s="2">
-        <v>46026.69665509259</v>
+        <v>46026.71429398148</v>
       </c>
       <c r="E272" s="2" t="s">
         <v>247</v>
@@ -9953,7 +9969,7 @@
         <v>272</v>
       </c>
       <c r="G272" s="2">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="H272" s="2">
         <v>0</v>
@@ -9970,22 +9986,22 @@
         <v>213</v>
       </c>
       <c r="B273" s="2">
-        <v>46026.33210648148</v>
+        <v>46026.32607638889</v>
       </c>
       <c r="C273" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D273" s="2">
-        <v>46026.56033564815</v>
+        <v>46026.50052083333</v>
       </c>
       <c r="E273" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F273" s="2" t="s">
         <v>272</v>
       </c>
       <c r="G273" s="2">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="H273" s="2">
         <v>0</v>
@@ -10002,13 +10018,13 @@
         <v>214</v>
       </c>
       <c r="B274" s="2">
-        <v>46026.31291666667</v>
+        <v>46026.5393287037</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D274" s="2">
-        <v>46026.46626157407</v>
+        <v>46026.71388888889</v>
       </c>
       <c r="E274" s="2" t="s">
         <v>247</v>
@@ -10017,7 +10033,7 @@
         <v>272</v>
       </c>
       <c r="G274" s="2">
-        <v>17.5</v>
+        <v>22.88</v>
       </c>
       <c r="H274" s="2">
         <v>0</v>
@@ -10031,16 +10047,16 @@
     </row>
     <row r="275" spans="1:10">
       <c r="A275" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B275" s="2">
-        <v>46026.33021990741</v>
+        <v>46026.33872685185</v>
       </c>
       <c r="C275" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D275" s="2">
-        <v>46026.54653935185</v>
+        <v>46026.52005787037</v>
       </c>
       <c r="E275" s="2" t="s">
         <v>248</v>
@@ -10049,7 +10065,7 @@
         <v>272</v>
       </c>
       <c r="G275" s="2">
-        <v>18.5</v>
+        <v>22.88</v>
       </c>
       <c r="H275" s="2">
         <v>0</v>
@@ -10063,25 +10079,25 @@
     </row>
     <row r="276" spans="1:10">
       <c r="A276" s="2" t="s">
-        <v>10</v>
+        <v>215</v>
       </c>
       <c r="B276" s="2">
-        <v>46026.33030092593</v>
+        <v>46026.54751157408</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D276" s="2">
-        <v>46026.54261574074</v>
+        <v>46026.69097222222</v>
       </c>
       <c r="E276" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F276" s="2" t="s">
         <v>272</v>
       </c>
       <c r="G276" s="2">
-        <v>18.5</v>
+        <v>25.34</v>
       </c>
       <c r="H276" s="2">
         <v>0</v>
@@ -10098,22 +10114,22 @@
         <v>215</v>
       </c>
       <c r="B277" s="2">
-        <v>46026.30677083333</v>
+        <v>46026.31126157408</v>
       </c>
       <c r="C277" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D277" s="2">
-        <v>46026.46386574074</v>
+        <v>46026.51475694445</v>
       </c>
       <c r="E277" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F277" s="2" t="s">
         <v>272</v>
       </c>
       <c r="G277" s="2">
-        <v>17</v>
+        <v>25.34</v>
       </c>
       <c r="H277" s="2">
         <v>0</v>
@@ -10127,16 +10143,16 @@
     </row>
     <row r="278" spans="1:10">
       <c r="A278" s="2" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B278" s="2">
-        <v>46026.53858796296</v>
+        <v>46026.52092592593</v>
       </c>
       <c r="C278" s="2" t="s">
         <v>243</v>
       </c>
       <c r="D278" s="2">
-        <v>46026.68185185185</v>
+        <v>46026.69629629629</v>
       </c>
       <c r="E278" s="2" t="s">
         <v>247</v>
@@ -10145,7 +10161,7 @@
         <v>272</v>
       </c>
       <c r="G278" s="2">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="H278" s="2">
         <v>0</v>
@@ -10159,25 +10175,25 @@
     </row>
     <row r="279" spans="1:10">
       <c r="A279" s="2" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="B279" s="2">
-        <v>46026.54040509259</v>
+        <v>46026.52128472222</v>
       </c>
       <c r="C279" s="2" t="s">
         <v>243</v>
       </c>
       <c r="D279" s="2">
-        <v>46026.68693287037</v>
+        <v>46026.71424768519</v>
       </c>
       <c r="E279" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F279" s="2" t="s">
         <v>272</v>
       </c>
       <c r="G279" s="2">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="H279" s="2">
         <v>0</v>
@@ -10191,25 +10207,25 @@
     </row>
     <row r="280" spans="1:10">
       <c r="A280" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B280" s="2">
-        <v>46026.31361111111</v>
+        <v>46026.53799768518</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D280" s="2">
-        <v>46026.50003472222</v>
+        <v>46026.68679398148</v>
       </c>
       <c r="E280" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F280" s="2" t="s">
         <v>272</v>
       </c>
       <c r="G280" s="2">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="H280" s="2">
         <v>0</v>
@@ -10223,16 +10239,16 @@
     </row>
     <row r="281" spans="1:10">
       <c r="A281" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B281" s="2">
-        <v>46026.32859953704</v>
+        <v>46026.32832175926</v>
       </c>
       <c r="C281" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D281" s="2">
-        <v>46026.50217592593</v>
+        <v>46026.49940972222</v>
       </c>
       <c r="E281" s="2" t="s">
         <v>248</v>
@@ -10241,7 +10257,7 @@
         <v>272</v>
       </c>
       <c r="G281" s="2">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="H281" s="2">
         <v>0</v>
@@ -10255,16 +10271,16 @@
     </row>
     <row r="282" spans="1:10">
       <c r="A282" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B282" s="2">
-        <v>46026.53799768518</v>
+        <v>46026.54040509259</v>
       </c>
       <c r="C282" s="2" t="s">
         <v>243</v>
       </c>
       <c r="D282" s="2">
-        <v>46026.68679398148</v>
+        <v>46026.68693287037</v>
       </c>
       <c r="E282" s="2" t="s">
         <v>247</v>
@@ -10273,7 +10289,7 @@
         <v>272</v>
       </c>
       <c r="G282" s="2">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="H282" s="2">
         <v>0</v>
@@ -10287,16 +10303,16 @@
     </row>
     <row r="283" spans="1:10">
       <c r="A283" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B283" s="2">
-        <v>46026.31226851852</v>
+        <v>46026.32859953704</v>
       </c>
       <c r="C283" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D283" s="2">
-        <v>46026.49762731481</v>
+        <v>46026.50217592593</v>
       </c>
       <c r="E283" s="2" t="s">
         <v>248</v>
@@ -10305,7 +10321,7 @@
         <v>272</v>
       </c>
       <c r="G283" s="2">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="H283" s="2">
         <v>0</v>
@@ -10319,16 +10335,16 @@
     </row>
     <row r="284" spans="1:10">
       <c r="A284" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B284" s="2">
-        <v>46026.32130787037</v>
+        <v>46026.53858796296</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D284" s="2">
-        <v>46026.55971064815</v>
+        <v>46026.68185185185</v>
       </c>
       <c r="E284" s="2" t="s">
         <v>247</v>
@@ -10337,7 +10353,7 @@
         <v>272</v>
       </c>
       <c r="G284" s="2">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="H284" s="2">
         <v>0</v>
@@ -10351,25 +10367,25 @@
     </row>
     <row r="285" spans="1:10">
       <c r="A285" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B285" s="2">
-        <v>46026.53828703704</v>
+        <v>46026.31226851852</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D285" s="2">
-        <v>46026.67511574074</v>
+        <v>46026.49762731481</v>
       </c>
       <c r="E285" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F285" s="2" t="s">
         <v>272</v>
       </c>
       <c r="G285" s="2">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="H285" s="2">
         <v>0</v>
@@ -10383,16 +10399,16 @@
     </row>
     <row r="286" spans="1:10">
       <c r="A286" s="2" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="B286" s="2">
-        <v>46026.32782407408</v>
+        <v>46026.31361111111</v>
       </c>
       <c r="C286" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D286" s="2">
-        <v>46026.5155787037</v>
+        <v>46026.50003472222</v>
       </c>
       <c r="E286" s="2" t="s">
         <v>248</v>
@@ -10401,7 +10417,7 @@
         <v>272</v>
       </c>
       <c r="G286" s="2">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="H286" s="2">
         <v>0</v>
@@ -10415,16 +10431,16 @@
     </row>
     <row r="287" spans="1:10">
       <c r="A287" s="2" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B287" s="2">
-        <v>46026.5381712963</v>
+        <v>46026.53828703704</v>
       </c>
       <c r="C287" s="2" t="s">
         <v>243</v>
       </c>
       <c r="D287" s="2">
-        <v>46026.68163194445</v>
+        <v>46026.67511574074</v>
       </c>
       <c r="E287" s="2" t="s">
         <v>247</v>
@@ -10433,7 +10449,7 @@
         <v>272</v>
       </c>
       <c r="G287" s="2">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="H287" s="2">
         <v>0</v>
@@ -10447,25 +10463,25 @@
     </row>
     <row r="288" spans="1:10">
       <c r="A288" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B288" s="2">
-        <v>46026.51545138889</v>
+        <v>46026.32130787037</v>
       </c>
       <c r="C288" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D288" s="2">
-        <v>46026.51547453704</v>
+        <v>46026.55971064815</v>
       </c>
       <c r="E288" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F288" s="2" t="s">
         <v>272</v>
       </c>
       <c r="G288" s="2">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="H288" s="2">
         <v>0</v>
@@ -10479,25 +10495,25 @@
     </row>
     <row r="289" spans="1:10">
       <c r="A289" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B289" s="2">
-        <v>46026.32832175926</v>
+        <v>46026.33210648148</v>
       </c>
       <c r="C289" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D289" s="2">
-        <v>46026.49940972222</v>
+        <v>46026.56033564815</v>
       </c>
       <c r="E289" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F289" s="2" t="s">
         <v>272</v>
       </c>
       <c r="G289" s="2">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="H289" s="2">
         <v>0</v>
@@ -10511,16 +10527,16 @@
     </row>
     <row r="290" spans="1:10">
       <c r="A290" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B290" s="2">
-        <v>46026.31456018519</v>
+        <v>46026.31291666667</v>
       </c>
       <c r="C290" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D290" s="2">
-        <v>46026.55396990741</v>
+        <v>46026.46626157407</v>
       </c>
       <c r="E290" s="2" t="s">
         <v>247</v>
@@ -10529,7 +10545,7 @@
         <v>272</v>
       </c>
       <c r="G290" s="2">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="H290" s="2">
         <v>0</v>
@@ -10543,25 +10559,25 @@
     </row>
     <row r="291" spans="1:10">
       <c r="A291" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B291" s="2">
-        <v>46026.5393287037</v>
+        <v>46026.33021990741</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D291" s="2">
-        <v>46026.71388888889</v>
+        <v>46026.54653935185</v>
       </c>
       <c r="E291" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F291" s="2" t="s">
         <v>272</v>
       </c>
       <c r="G291" s="2">
-        <v>22.88</v>
+        <v>18.5</v>
       </c>
       <c r="H291" s="2">
         <v>0</v>
@@ -10575,25 +10591,25 @@
     </row>
     <row r="292" spans="1:10">
       <c r="A292" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B292" s="2">
-        <v>46026.33872685185</v>
+        <v>46026.58375</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D292" s="2">
-        <v>46026.52005787037</v>
+        <v>46026.69665509259</v>
       </c>
       <c r="E292" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F292" s="2" t="s">
         <v>272</v>
       </c>
       <c r="G292" s="2">
-        <v>22.88</v>
+        <v>18.5</v>
       </c>
       <c r="H292" s="2">
         <v>0</v>
@@ -10607,25 +10623,25 @@
     </row>
     <row r="293" spans="1:10">
       <c r="A293" s="2" t="s">
-        <v>225</v>
+        <v>10</v>
       </c>
       <c r="B293" s="2">
-        <v>46026.54751157408</v>
+        <v>46026.33030092593</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D293" s="2">
-        <v>46026.69097222222</v>
+        <v>46026.54261574074</v>
       </c>
       <c r="E293" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F293" s="2" t="s">
         <v>272</v>
       </c>
       <c r="G293" s="2">
-        <v>25.34</v>
+        <v>18.5</v>
       </c>
       <c r="H293" s="2">
         <v>0</v>
@@ -10639,25 +10655,25 @@
     </row>
     <row r="294" spans="1:10">
       <c r="A294" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B294" s="2">
-        <v>46026.31126157408</v>
+        <v>46026.31456018519</v>
       </c>
       <c r="C294" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D294" s="2">
-        <v>46026.51475694445</v>
+        <v>46026.55396990741</v>
       </c>
       <c r="E294" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F294" s="2" t="s">
         <v>272</v>
       </c>
       <c r="G294" s="2">
-        <v>25.34</v>
+        <v>17</v>
       </c>
       <c r="H294" s="2">
         <v>0</v>
@@ -10671,16 +10687,16 @@
     </row>
     <row r="295" spans="1:10">
       <c r="A295" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B295" s="2">
-        <v>46026.52092592593</v>
+        <v>46026.30677083333</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D295" s="2">
-        <v>46026.69629629629</v>
+        <v>46026.46386574074</v>
       </c>
       <c r="E295" s="2" t="s">
         <v>247</v>
@@ -10689,7 +10705,7 @@
         <v>272</v>
       </c>
       <c r="G295" s="2">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="H295" s="2">
         <v>0</v>
@@ -10706,22 +10722,22 @@
         <v>226</v>
       </c>
       <c r="B296" s="2">
-        <v>46026.32607638889</v>
+        <v>46026.33194444444</v>
       </c>
       <c r="C296" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D296" s="2">
-        <v>46026.50052083333</v>
+        <v>46026.51525462963</v>
       </c>
       <c r="E296" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F296" s="2" t="s">
         <v>272</v>
       </c>
       <c r="G296" s="2">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="H296" s="2">
         <v>0</v>
@@ -10735,25 +10751,25 @@
     </row>
     <row r="297" spans="1:10">
       <c r="A297" s="2" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="B297" s="2">
-        <v>46026.71427083333</v>
+        <v>46026.51545138889</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D297" s="2">
-        <v>46026.71429398148</v>
+        <v>46026.51547453704</v>
       </c>
       <c r="E297" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F297" s="2" t="s">
         <v>272</v>
       </c>
       <c r="G297" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H297" s="2">
         <v>0</v>
@@ -10767,25 +10783,25 @@
     </row>
     <row r="298" spans="1:10">
       <c r="A298" s="2" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="B298" s="2">
-        <v>46026.52128472222</v>
+        <v>46026.5381712963</v>
       </c>
       <c r="C298" s="2" t="s">
         <v>243</v>
       </c>
       <c r="D298" s="2">
-        <v>46026.71424768519</v>
+        <v>46026.68163194445</v>
       </c>
       <c r="E298" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F298" s="2" t="s">
         <v>272</v>
       </c>
       <c r="G298" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H298" s="2">
         <v>0</v>
@@ -10799,25 +10815,25 @@
     </row>
     <row r="299" spans="1:10">
       <c r="A299" s="2" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B299" s="2">
-        <v>46026.33194444444</v>
+        <v>46026.32782407408</v>
       </c>
       <c r="C299" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D299" s="2">
-        <v>46026.51525462963</v>
+        <v>46026.5155787037</v>
       </c>
       <c r="E299" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F299" s="2" t="s">
         <v>272</v>
       </c>
       <c r="G299" s="2">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="H299" s="2">
         <v>0</v>
@@ -10834,13 +10850,13 @@
         <v>227</v>
       </c>
       <c r="B300" s="2">
-        <v>46026.65186342593</v>
+        <v>46026.48775462963</v>
       </c>
       <c r="C300" s="2" t="s">
         <v>243</v>
       </c>
       <c r="D300" s="2">
-        <v>46026.70450231482</v>
+        <v>46026.62233796297</v>
       </c>
       <c r="E300" s="2" t="s">
         <v>247</v>
@@ -10849,7 +10865,7 @@
         <v>273</v>
       </c>
       <c r="G300" s="2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H300" s="2">
         <v>0</v>
@@ -10863,16 +10879,16 @@
     </row>
     <row r="301" spans="1:10">
       <c r="A301" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B301" s="2">
-        <v>46026.27144675926</v>
+        <v>46026.27120370371</v>
       </c>
       <c r="C301" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D301" s="2">
-        <v>46026.52704861111</v>
+        <v>46026.46472222222</v>
       </c>
       <c r="E301" s="2" t="s">
         <v>248</v>
@@ -10881,7 +10897,7 @@
         <v>273</v>
       </c>
       <c r="G301" s="2">
-        <v>17.5</v>
+        <v>26</v>
       </c>
       <c r="H301" s="2">
         <v>0</v>
@@ -10898,13 +10914,13 @@
         <v>228</v>
       </c>
       <c r="B302" s="2">
-        <v>46026.55230324074</v>
+        <v>46026.54887731482</v>
       </c>
       <c r="C302" s="2" t="s">
         <v>243</v>
       </c>
       <c r="D302" s="2">
-        <v>46026.77086805556</v>
+        <v>46026.71451388889</v>
       </c>
       <c r="E302" s="2" t="s">
         <v>247</v>
@@ -10913,7 +10929,7 @@
         <v>273</v>
       </c>
       <c r="G302" s="2">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="H302" s="2">
         <v>0</v>
@@ -10927,7 +10943,7 @@
     </row>
     <row r="303" spans="1:10">
       <c r="A303" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B303" s="2">
         <v>46026.33210648148</v>
@@ -10962,13 +10978,13 @@
         <v>229</v>
       </c>
       <c r="B304" s="2">
-        <v>46026.54887731482</v>
+        <v>46026.54028935185</v>
       </c>
       <c r="C304" s="2" t="s">
         <v>243</v>
       </c>
       <c r="D304" s="2">
-        <v>46026.71451388889</v>
+        <v>46026.76541666667</v>
       </c>
       <c r="E304" s="2" t="s">
         <v>247</v>
@@ -10977,7 +10993,7 @@
         <v>273</v>
       </c>
       <c r="G304" s="2">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H304" s="2">
         <v>0</v>
@@ -10991,16 +11007,16 @@
     </row>
     <row r="305" spans="1:10">
       <c r="A305" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B305" s="2">
-        <v>46026.27120370371</v>
+        <v>46026.30401620371</v>
       </c>
       <c r="C305" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D305" s="2">
-        <v>46026.46472222222</v>
+        <v>46026.51929398148</v>
       </c>
       <c r="E305" s="2" t="s">
         <v>248</v>
@@ -11023,16 +11039,16 @@
     </row>
     <row r="306" spans="1:10">
       <c r="A306" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B306" s="2">
-        <v>46026.54028935185</v>
+        <v>46026.57717592592</v>
       </c>
       <c r="C306" s="2" t="s">
         <v>243</v>
       </c>
       <c r="D306" s="2">
-        <v>46026.76541666667</v>
+        <v>46026.70792824074</v>
       </c>
       <c r="E306" s="2" t="s">
         <v>247</v>
@@ -11041,7 +11057,7 @@
         <v>273</v>
       </c>
       <c r="G306" s="2">
-        <v>26</v>
+        <v>17.5</v>
       </c>
       <c r="H306" s="2">
         <v>0</v>
@@ -11055,19 +11071,19 @@
     </row>
     <row r="307" spans="1:10">
       <c r="A307" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B307" s="2">
-        <v>46026.27540509259</v>
+        <v>46026.52045138889</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D307" s="2">
-        <v>46026.49458333333</v>
+        <v>46026.73671296296</v>
       </c>
       <c r="E307" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F307" s="2" t="s">
         <v>273</v>
@@ -11090,16 +11106,16 @@
         <v>232</v>
       </c>
       <c r="B308" s="2">
-        <v>46026.52045138889</v>
+        <v>46026.27144675926</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D308" s="2">
-        <v>46026.73671296296</v>
+        <v>46026.52704861111</v>
       </c>
       <c r="E308" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F308" s="2" t="s">
         <v>273</v>
@@ -11119,16 +11135,16 @@
     </row>
     <row r="309" spans="1:10">
       <c r="A309" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B309" s="2">
-        <v>46026.3312037037</v>
+        <v>46026.27540509259</v>
       </c>
       <c r="C309" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D309" s="2">
-        <v>46026.46556712963</v>
+        <v>46026.49458333333</v>
       </c>
       <c r="E309" s="2" t="s">
         <v>248</v>
@@ -11137,7 +11153,7 @@
         <v>273</v>
       </c>
       <c r="G309" s="2">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="H309" s="2">
         <v>0</v>
@@ -11154,22 +11170,22 @@
         <v>233</v>
       </c>
       <c r="B310" s="2">
-        <v>46026.33384259259</v>
+        <v>46026.65186342593</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D310" s="2">
-        <v>46026.55581018519</v>
+        <v>46026.70450231482</v>
       </c>
       <c r="E310" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F310" s="2" t="s">
         <v>273</v>
       </c>
       <c r="G310" s="2">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="H310" s="2">
         <v>0</v>
@@ -11186,22 +11202,22 @@
         <v>233</v>
       </c>
       <c r="B311" s="2">
-        <v>46026.57717592592</v>
+        <v>46026.3312037037</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D311" s="2">
-        <v>46026.70792824074</v>
+        <v>46026.46556712963</v>
       </c>
       <c r="E311" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F311" s="2" t="s">
         <v>273</v>
       </c>
       <c r="G311" s="2">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="H311" s="2">
         <v>0</v>
@@ -11215,16 +11231,16 @@
     </row>
     <row r="312" spans="1:10">
       <c r="A312" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B312" s="2">
-        <v>46026.30401620371</v>
+        <v>46026.33384259259</v>
       </c>
       <c r="C312" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D312" s="2">
-        <v>46026.51929398148</v>
+        <v>46026.55581018519</v>
       </c>
       <c r="E312" s="2" t="s">
         <v>248</v>
@@ -11233,7 +11249,7 @@
         <v>273</v>
       </c>
       <c r="G312" s="2">
-        <v>26</v>
+        <v>17.5</v>
       </c>
       <c r="H312" s="2">
         <v>0</v>
@@ -11247,16 +11263,16 @@
     </row>
     <row r="313" spans="1:10">
       <c r="A313" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B313" s="2">
-        <v>46026.48775462963</v>
+        <v>46026.55230324074</v>
       </c>
       <c r="C313" s="2" t="s">
         <v>243</v>
       </c>
       <c r="D313" s="2">
-        <v>46026.62233796297</v>
+        <v>46026.77086805556</v>
       </c>
       <c r="E313" s="2" t="s">
         <v>247</v>
@@ -11265,7 +11281,7 @@
         <v>273</v>
       </c>
       <c r="G313" s="2">
-        <v>26</v>
+        <v>17.5</v>
       </c>
       <c r="H313" s="2">
         <v>0</v>
@@ -11282,13 +11298,13 @@
         <v>234</v>
       </c>
       <c r="B314" s="2">
-        <v>46026.45023148148</v>
+        <v>46026.31866898148</v>
       </c>
       <c r="C314" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D314" s="2">
-        <v>46026.60083333333</v>
+        <v>46026.71444444444</v>
       </c>
       <c r="E314" s="2" t="s">
         <v>247</v>
@@ -11297,7 +11313,7 @@
         <v>274</v>
       </c>
       <c r="G314" s="2">
-        <v>22.09</v>
+        <v>24.25</v>
       </c>
       <c r="H314" s="2">
         <v>0</v>
@@ -11314,13 +11330,13 @@
         <v>235</v>
       </c>
       <c r="B315" s="2">
-        <v>46026.31866898148</v>
+        <v>46026.45023148148</v>
       </c>
       <c r="C315" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D315" s="2">
-        <v>46026.71444444444</v>
+        <v>46026.60083333333</v>
       </c>
       <c r="E315" s="2" t="s">
         <v>247</v>
@@ -11329,7 +11345,7 @@
         <v>274</v>
       </c>
       <c r="G315" s="2">
-        <v>24.25</v>
+        <v>22.09</v>
       </c>
       <c r="H315" s="2">
         <v>0</v>
